--- a/songs.xlsx
+++ b/songs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
   <si>
     <t>id</t>
   </si>
@@ -40,19 +40,19 @@
     <t>note</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
+    <t>https://www.youtube.com/watch?v=PZN1ns6OIyc</t>
   </si>
   <si>
     <t>47:01</t>
   </si>
   <si>
     <t>含淚跳恰恰</t>
-  </si>
-  <si>
-    <t>https://www.youtube.com/watch?v=PZN1ns6OIyc</t>
   </si>
   <si>
     <t>謝金燕</t>
@@ -70,13 +70,19 @@
     <t>BAD GUY</t>
   </si>
   <si>
-    <t>ACT/アクト</t>
-  </si>
-  <si>
     <t>Billie Eilish</t>
   </si>
   <si>
     <t>Cover</t>
+  </si>
+  <si>
+    <t>大笑之歌</t>
+  </si>
+  <si>
+    <t>ACT/アクト</t>
+  </si>
+  <si>
+    <t>四千金</t>
   </si>
   <si>
     <t>Giga, TeddyLoid, Daoko</t>
@@ -85,7 +91,16 @@
     <t>32:29</t>
   </si>
   <si>
+    <t>7:16</t>
+  </si>
+  <si>
+    <t>藍</t>
+  </si>
+  <si>
     <t>JANE DOE</t>
+  </si>
+  <si>
+    <t>石白其</t>
   </si>
   <si>
     <t>米津玄師, 宇多田ヒカル</t>
@@ -94,31 +109,10 @@
     <t>NG</t>
   </si>
   <si>
-    <t>大笑之歌</t>
+    <t>11:44</t>
   </si>
   <si>
     <t>33:52</t>
-  </si>
-  <si>
-    <t>四千金</t>
-  </si>
-  <si>
-    <t>7:16</t>
-  </si>
-  <si>
-    <t>34:58</t>
-  </si>
-  <si>
-    <t>藍</t>
-  </si>
-  <si>
-    <t>石白其</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>37:38</t>
   </si>
   <si>
     <t>17:34</t>
@@ -130,16 +124,10 @@
     <t>郁可唯</t>
   </si>
   <si>
-    <t>40:59</t>
-  </si>
-  <si>
-    <t>IRIS OUT</t>
+    <t>34:58</t>
   </si>
   <si>
     <t>21:56</t>
-  </si>
-  <si>
-    <t>米津玄師</t>
   </si>
   <si>
     <t>半句再見</t>
@@ -148,10 +136,10 @@
     <t>孫燕姿</t>
   </si>
   <si>
-    <t>42:09</t>
+    <t>26:23</t>
   </si>
   <si>
-    <t>26:23</t>
+    <t>37:38</t>
   </si>
   <si>
     <t>慢冷</t>
@@ -160,22 +148,22 @@
     <t>梁靜茹</t>
   </si>
   <si>
+    <t>40:59</t>
+  </si>
+  <si>
     <t>52:08</t>
   </si>
   <si>
-    <t>44:43</t>
-  </si>
-  <si>
-    <t>革命道中</t>
+    <t>IRIS OUT</t>
   </si>
   <si>
     <t>孤獨的總和</t>
   </si>
   <si>
-    <t>アイナ・ジ・エンド</t>
+    <t>吳汶芳</t>
   </si>
   <si>
-    <t>吳汶芳</t>
+    <t>米津玄師</t>
   </si>
   <si>
     <t>57:34</t>
@@ -211,6 +199,9 @@
     <t>開始懂了</t>
   </si>
   <si>
+    <t>42:09</t>
+  </si>
+  <si>
     <t>1:17:44</t>
   </si>
   <si>
@@ -227,6 +218,24 @@
   </si>
   <si>
     <t>我懷念的</t>
+  </si>
+  <si>
+    <t>44:43</t>
+  </si>
+  <si>
+    <t>革命道中</t>
+  </si>
+  <si>
+    <t>4:15:50</t>
+  </si>
+  <si>
+    <t>我們不一樣</t>
+  </si>
+  <si>
+    <t>大壯</t>
+  </si>
+  <si>
+    <t>アイナ・ジ・エンド</t>
   </si>
 </sst>
 </file>
@@ -538,17 +547,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -559,13 +568,13 @@
         <v>24.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -576,13 +585,13 @@
         <v>24.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -593,13 +602,13 @@
         <v>24.0</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -610,13 +619,13 @@
         <v>24.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -627,13 +636,13 @@
         <v>24.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -644,13 +653,13 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="9">
@@ -661,16 +670,16 @@
         <v>24.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -681,13 +690,13 @@
         <v>24.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -698,13 +707,13 @@
         <v>24.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -715,13 +724,13 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -732,16 +741,16 @@
         <v>24.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -752,13 +761,13 @@
         <v>24.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
@@ -769,14 +778,55 @@
         <v>24.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="E16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="D17" s="4"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19">
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20">
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="D21" s="4"/>
+    </row>
+    <row r="22">
+      <c r="D22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24">
+      <c r="D24" s="4"/>
     </row>
     <row r="25">
       <c r="D25" s="4"/>
@@ -3755,17 +3805,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -6808,17 +6858,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -6829,16 +6879,16 @@
         <v>24.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -6849,16 +6899,16 @@
         <v>24.0</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -6869,16 +6919,16 @@
         <v>24.0</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -6889,16 +6939,16 @@
         <v>24.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -6909,16 +6959,16 @@
         <v>24.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -6929,16 +6979,16 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -6949,16 +6999,16 @@
         <v>24.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -9983,10 +10033,10 @@
         <v>24.0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>

--- a/songs.xlsx
+++ b/songs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="247">
   <si>
     <t>id</t>
   </si>
@@ -40,18 +40,18 @@
     <t>note</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=PZN1ns6OIyc</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
   </si>
   <si>
+    <t>47:01</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=PZN1ns6OIyc</t>
-  </si>
-  <si>
-    <t>47:01</t>
-  </si>
-  <si>
     <t>含淚跳恰恰</t>
   </si>
   <si>
@@ -67,117 +67,177 @@
     <t>施文彬</t>
   </si>
   <si>
+    <t>6:01:13</t>
+  </si>
+  <si>
+    <t>香水</t>
+  </si>
+  <si>
+    <t>江志豐 vs 張秀卿</t>
+  </si>
+  <si>
+    <t>切歌</t>
+  </si>
+  <si>
+    <t>6:09:58</t>
+  </si>
+  <si>
+    <t>浪子回頭</t>
+  </si>
+  <si>
+    <t>茄子蛋</t>
+  </si>
+  <si>
+    <t>4:27:49</t>
+  </si>
+  <si>
+    <t>我是恁老爸</t>
+  </si>
+  <si>
+    <t>猪哥亮</t>
+  </si>
+  <si>
+    <t>大笑之歌</t>
+  </si>
+  <si>
     <t>BAD GUY</t>
   </si>
   <si>
+    <t>四千金</t>
+  </si>
+  <si>
+    <t>ACT/アクト</t>
+  </si>
+  <si>
     <t>Billie Eilish</t>
   </si>
   <si>
     <t>Cover</t>
   </si>
   <si>
-    <t>大笑之歌</t>
-  </si>
-  <si>
-    <t>ACT/アクト</t>
-  </si>
-  <si>
-    <t>四千金</t>
-  </si>
-  <si>
     <t>Giga, TeddyLoid, Daoko</t>
   </si>
   <si>
+    <t>7:16</t>
+  </si>
+  <si>
+    <t>藍</t>
+  </si>
+  <si>
+    <t>4:44:17</t>
+  </si>
+  <si>
+    <t>石白其</t>
+  </si>
+  <si>
+    <t>wish you were gay</t>
+  </si>
+  <si>
     <t>32:29</t>
   </si>
   <si>
-    <t>7:16</t>
-  </si>
-  <si>
-    <t>藍</t>
-  </si>
-  <si>
     <t>JANE DOE</t>
   </si>
   <si>
-    <t>石白其</t>
-  </si>
-  <si>
     <t>米津玄師, 宇多田ヒカル</t>
   </si>
   <si>
+    <t>11:44</t>
+  </si>
+  <si>
     <t>NG</t>
   </si>
   <si>
-    <t>11:44</t>
+    <t>4:48:35</t>
+  </si>
+  <si>
+    <t>i love you</t>
+  </si>
+  <si>
+    <t>17:34</t>
   </si>
   <si>
     <t>33:52</t>
   </si>
   <si>
-    <t>17:34</t>
-  </si>
-  <si>
     <t>路過人間</t>
   </si>
   <si>
+    <t>5:04:18</t>
+  </si>
+  <si>
     <t>郁可唯</t>
   </si>
   <si>
+    <t>CoCo</t>
+  </si>
+  <si>
+    <t>O.T. Genasis</t>
+  </si>
+  <si>
+    <t>21:56</t>
+  </si>
+  <si>
+    <t>半句再見</t>
+  </si>
+  <si>
+    <t>孫燕姿</t>
+  </si>
+  <si>
+    <t>4:06:47</t>
+  </si>
+  <si>
     <t>34:58</t>
   </si>
   <si>
-    <t>21:56</t>
-  </si>
-  <si>
-    <t>半句再見</t>
-  </si>
-  <si>
-    <t>孫燕姿</t>
+    <t>Playground</t>
+  </si>
+  <si>
+    <t>Bea Miller</t>
   </si>
   <si>
     <t>26:23</t>
   </si>
   <si>
+    <t>慢冷</t>
+  </si>
+  <si>
+    <t>梁靜茹</t>
+  </si>
+  <si>
     <t>37:38</t>
   </si>
   <si>
-    <t>慢冷</t>
-  </si>
-  <si>
-    <t>梁靜茹</t>
+    <t>52:08</t>
+  </si>
+  <si>
+    <t>孤獨的總和</t>
+  </si>
+  <si>
+    <t>吳汶芳</t>
+  </si>
+  <si>
+    <t>57:34</t>
+  </si>
+  <si>
+    <t>挪威的森林</t>
   </si>
   <si>
     <t>40:59</t>
   </si>
   <si>
-    <t>52:08</t>
+    <t>伍佰</t>
   </si>
   <si>
     <t>IRIS OUT</t>
   </si>
   <si>
-    <t>孤獨的總和</t>
-  </si>
-  <si>
-    <t>吳汶芳</t>
+    <t>觀眾唱</t>
   </si>
   <si>
     <t>米津玄師</t>
   </si>
   <si>
-    <t>57:34</t>
-  </si>
-  <si>
-    <t>挪威的森林</t>
-  </si>
-  <si>
-    <t>伍佰</t>
-  </si>
-  <si>
-    <t>觀眾唱</t>
-  </si>
-  <si>
     <t>1:03:45</t>
   </si>
   <si>
@@ -187,19 +247,28 @@
     <t>魏如萱</t>
   </si>
   <si>
+    <t>42:09</t>
+  </si>
+  <si>
     <t>1:08:09</t>
   </si>
   <si>
     <t>我在紐約打電話給你</t>
   </si>
   <si>
+    <t>44:43</t>
+  </si>
+  <si>
     <t>1:12:27</t>
   </si>
   <si>
+    <t>革命道中</t>
+  </si>
+  <si>
     <t>開始懂了</t>
   </si>
   <si>
-    <t>42:09</t>
+    <t>アイナ・ジ・エンド</t>
   </si>
   <si>
     <t>1:17:44</t>
@@ -208,34 +277,484 @@
     <t>我不難過</t>
   </si>
   <si>
-    <t>切歌</t>
+    <t>4:20:12</t>
+  </si>
+  <si>
+    <t>​​Bunny Girl</t>
+  </si>
+  <si>
+    <t>AKASAKI</t>
   </si>
   <si>
     <t>1:18:47</t>
   </si>
   <si>
+    <t>4:24:52</t>
+  </si>
+  <si>
+    <t>プロポーズ</t>
+  </si>
+  <si>
     <t>1:25:12</t>
   </si>
   <si>
+    <t>なとり</t>
+  </si>
+  <si>
     <t>我懷念的</t>
   </si>
   <si>
-    <t>44:43</t>
-  </si>
-  <si>
-    <t>革命道中</t>
-  </si>
-  <si>
     <t>4:15:50</t>
   </si>
   <si>
+    <t>4:27:12</t>
+  </si>
+  <si>
     <t>我們不一樣</t>
   </si>
   <si>
+    <t>鬼ノ宴(Demons Banquet)</t>
+  </si>
+  <si>
     <t>大壯</t>
   </si>
   <si>
-    <t>アイナ・ジ・エンド</t>
+    <t>友成空</t>
+  </si>
+  <si>
+    <t>4:18:46</t>
+  </si>
+  <si>
+    <t>因為單身的緣故</t>
+  </si>
+  <si>
+    <t>李宗盛</t>
+  </si>
+  <si>
+    <t>4:29:40</t>
+  </si>
+  <si>
+    <t>ほろよい</t>
+  </si>
+  <si>
+    <t>さんひ</t>
+  </si>
+  <si>
+    <t>4:53:54</t>
+  </si>
+  <si>
+    <t>4:59:15</t>
+  </si>
+  <si>
+    <t>4:32:59</t>
+  </si>
+  <si>
+    <t>微加幸福</t>
+  </si>
+  <si>
+    <t>Overdose</t>
+  </si>
+  <si>
+    <t>5:47:00</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>?te 壞特</t>
+  </si>
+  <si>
+    <t>4:35:26</t>
+  </si>
+  <si>
+    <t>5:49:00</t>
+  </si>
+  <si>
+    <t>東京フラッシュ</t>
+  </si>
+  <si>
+    <t>Vaundy</t>
+  </si>
+  <si>
+    <t>5:58:06</t>
+  </si>
+  <si>
+    <t>體面</t>
+  </si>
+  <si>
+    <t>于文文</t>
+  </si>
+  <si>
+    <t>4:38:47</t>
+  </si>
+  <si>
+    <t>踊り子</t>
+  </si>
+  <si>
+    <t>6:05:24</t>
+  </si>
+  <si>
+    <t>捲菸</t>
+  </si>
+  <si>
+    <t>美秀集團</t>
+  </si>
+  <si>
+    <t>6:11:14</t>
+  </si>
+  <si>
+    <t>5:10:38</t>
+  </si>
+  <si>
+    <t>6:13:40</t>
+  </si>
+  <si>
+    <t>5:14:05</t>
+  </si>
+  <si>
+    <t>6:18:16</t>
+  </si>
+  <si>
+    <t>6:24:26</t>
+  </si>
+  <si>
+    <t>刻在我心底的名字</t>
+  </si>
+  <si>
+    <t>盧廣仲</t>
+  </si>
+  <si>
+    <t>5:15:38</t>
+  </si>
+  <si>
+    <t>6:36:21</t>
+  </si>
+  <si>
+    <t>幾分之幾</t>
+  </si>
+  <si>
+    <t>盧廣仲 / 花甲大人轉男孩</t>
+  </si>
+  <si>
+    <t>6:46:04</t>
+  </si>
+  <si>
+    <t>明明就</t>
+  </si>
+  <si>
+    <t>周杰倫</t>
+  </si>
+  <si>
+    <t>5:20:33</t>
+  </si>
+  <si>
+    <t>偽顔</t>
+  </si>
+  <si>
+    <t>6:53:33</t>
+  </si>
+  <si>
+    <t>yama</t>
+  </si>
+  <si>
+    <t>7:03:34</t>
+  </si>
+  <si>
+    <t>7:08:22</t>
+  </si>
+  <si>
+    <t>5:21:48</t>
+  </si>
+  <si>
+    <t>偽顏</t>
+  </si>
+  <si>
+    <t>39:47</t>
+  </si>
+  <si>
+    <t>寂寞寂寞就好</t>
+  </si>
+  <si>
+    <t>田馥甄</t>
+  </si>
+  <si>
+    <t>45:02</t>
+  </si>
+  <si>
+    <t>5:26:07</t>
+  </si>
+  <si>
+    <t>51:24</t>
+  </si>
+  <si>
+    <t>カタオモイ</t>
+  </si>
+  <si>
+    <t>倒帶</t>
+  </si>
+  <si>
+    <t>蔡依林</t>
+  </si>
+  <si>
+    <t>Aimer</t>
+  </si>
+  <si>
+    <t>56:42</t>
+  </si>
+  <si>
+    <t>5:28:28</t>
+  </si>
+  <si>
+    <t>1:02:53</t>
+  </si>
+  <si>
+    <t>NIGHT DANCER</t>
+  </si>
+  <si>
+    <t>imase</t>
+  </si>
+  <si>
+    <t>1:14:02</t>
+  </si>
+  <si>
+    <t>知道</t>
+  </si>
+  <si>
+    <t>郭靜</t>
+  </si>
+  <si>
+    <t>5:35:39</t>
+  </si>
+  <si>
+    <t>どうせ無くなるだけ</t>
+  </si>
+  <si>
+    <t>1:19:07</t>
+  </si>
+  <si>
+    <t>曖昧</t>
+  </si>
+  <si>
+    <t>たかやん</t>
+  </si>
+  <si>
+    <t>楊丞琳</t>
+  </si>
+  <si>
+    <t>1:26:53</t>
+  </si>
+  <si>
+    <t>小幸運</t>
+  </si>
+  <si>
+    <t>5:41:14</t>
+  </si>
+  <si>
+    <t>怪獣の花唄</t>
+  </si>
+  <si>
+    <t>1:33:50</t>
+  </si>
+  <si>
+    <t>喜劇收場</t>
+  </si>
+  <si>
+    <t>1:40:01</t>
+  </si>
+  <si>
+    <t>5:43:10</t>
+  </si>
+  <si>
+    <t>不夠成熟</t>
+  </si>
+  <si>
+    <t>BY2</t>
+  </si>
+  <si>
+    <t>ドライフラワー</t>
+  </si>
+  <si>
+    <t>優里</t>
+  </si>
+  <si>
+    <t>1:47:22</t>
+  </si>
+  <si>
+    <t>分手後不要做朋友</t>
+  </si>
+  <si>
+    <t>梁文音</t>
+  </si>
+  <si>
+    <t>1:59:55</t>
+  </si>
+  <si>
+    <t>5:52:55</t>
+  </si>
+  <si>
+    <t>我不配</t>
+  </si>
+  <si>
+    <t>不可幸力</t>
+  </si>
+  <si>
+    <t>2:05:01</t>
+  </si>
+  <si>
+    <t>2:14:03</t>
+  </si>
+  <si>
+    <t>老鼠愛大米</t>
+  </si>
+  <si>
+    <t>王啟文</t>
+  </si>
+  <si>
+    <t>2:16:55</t>
+  </si>
+  <si>
+    <t>下一個天亮</t>
+  </si>
+  <si>
+    <t>2:22:12</t>
+  </si>
+  <si>
+    <t>像天堂的懸崖</t>
+  </si>
+  <si>
+    <t>李佳薇</t>
+  </si>
+  <si>
+    <t>2:27:49</t>
+  </si>
+  <si>
+    <t>有一種悲傷</t>
+  </si>
+  <si>
+    <t>A-Lin</t>
+  </si>
+  <si>
+    <t>2:35:24</t>
+  </si>
+  <si>
+    <t>聽見下雨的聲音</t>
+  </si>
+  <si>
+    <t>魏如昀</t>
+  </si>
+  <si>
+    <t>2:40:30</t>
+  </si>
+  <si>
+    <t>落雨聲</t>
+  </si>
+  <si>
+    <t>江蕙</t>
+  </si>
+  <si>
+    <t>2:50:00</t>
+  </si>
+  <si>
+    <t>你就不要想起我</t>
+  </si>
+  <si>
+    <t>2:54:45</t>
+  </si>
+  <si>
+    <t>3:00:18</t>
+  </si>
+  <si>
+    <t>3:11:22</t>
+  </si>
+  <si>
+    <t>3:22:00</t>
+  </si>
+  <si>
+    <t>雨愛</t>
+  </si>
+  <si>
+    <t>4:01:19</t>
+  </si>
+  <si>
+    <t>4:09:57</t>
+  </si>
+  <si>
+    <t>渺小</t>
+  </si>
+  <si>
+    <t>5:56:05</t>
+  </si>
+  <si>
+    <t>逆さまの蝶</t>
+  </si>
+  <si>
+    <t>SNoW / 地獄少女OP</t>
+  </si>
+  <si>
+    <t>4:16:28</t>
+  </si>
+  <si>
+    <t>我想我不會愛你</t>
+  </si>
+  <si>
+    <t>6:03:12</t>
+  </si>
+  <si>
+    <t>4:19:07</t>
+  </si>
+  <si>
+    <t>年輪說</t>
+  </si>
+  <si>
+    <t>瑛人</t>
+  </si>
+  <si>
+    <t>4:23:01</t>
+  </si>
+  <si>
+    <t>3:29:16</t>
+  </si>
+  <si>
+    <t>夢醒時分</t>
+  </si>
+  <si>
+    <t>白日</t>
+  </si>
+  <si>
+    <t>King Gnu</t>
+  </si>
+  <si>
+    <t>3:30:42</t>
+  </si>
+  <si>
+    <t>逢いたくていま</t>
+  </si>
+  <si>
+    <t>MISIA</t>
+  </si>
+  <si>
+    <t>3:39:48</t>
+  </si>
+  <si>
+    <t>ホウキ雲</t>
+  </si>
+  <si>
+    <t>RYTHEM / 烘焙王OP</t>
+  </si>
+  <si>
+    <t>3:43:29</t>
+  </si>
+  <si>
+    <t>3:48:22</t>
+  </si>
+  <si>
+    <t>3:53:31</t>
+  </si>
+  <si>
+    <t>3:55:11</t>
+  </si>
+  <si>
+    <t>Bunny Girl</t>
   </si>
 </sst>
 </file>
@@ -547,17 +1066,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -568,13 +1087,13 @@
         <v>24.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -585,13 +1104,13 @@
         <v>24.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -602,13 +1121,13 @@
         <v>24.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -619,13 +1138,13 @@
         <v>24.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -636,13 +1155,13 @@
         <v>24.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -653,13 +1172,13 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9">
@@ -670,16 +1189,16 @@
         <v>24.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -690,13 +1209,13 @@
         <v>24.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -707,13 +1226,13 @@
         <v>24.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12">
@@ -724,13 +1243,13 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13">
@@ -741,16 +1260,16 @@
         <v>24.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -761,13 +1280,13 @@
         <v>24.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -778,13 +1297,13 @@
         <v>24.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -792,179 +1311,812 @@
         <v>15.0</v>
       </c>
       <c r="C16" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="C32" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="C33" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="C34" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="C35" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="C36" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1">
         <v>42.0</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="C43" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1">
+        <v>46.0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1">
+        <v>47.0</v>
+      </c>
+      <c r="C48" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1">
+        <v>48.0</v>
+      </c>
+      <c r="C49" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1">
+        <v>49.0</v>
+      </c>
+      <c r="C50" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1">
+        <v>50.0</v>
+      </c>
+      <c r="C51" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1">
+        <v>51.0</v>
+      </c>
+      <c r="C52" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1">
+        <v>52.0</v>
+      </c>
+      <c r="C53" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1">
+        <v>53.0</v>
+      </c>
+      <c r="C54" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1">
+        <v>54.0</v>
+      </c>
+      <c r="C55" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1">
+        <v>55.0</v>
+      </c>
+      <c r="C56" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1">
+        <v>56.0</v>
+      </c>
+      <c r="C57" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1">
+        <v>57.0</v>
+      </c>
+      <c r="C58" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1">
+        <v>58.0</v>
+      </c>
+      <c r="C59" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="C60" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="C61" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="G61" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19">
-      <c r="D19" s="4"/>
-    </row>
-    <row r="20">
-      <c r="D20" s="4"/>
-    </row>
-    <row r="21">
-      <c r="D21" s="4"/>
-    </row>
-    <row r="22">
-      <c r="D22" s="4"/>
-    </row>
-    <row r="23">
-      <c r="D23" s="4"/>
-    </row>
-    <row r="24">
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25">
-      <c r="D25" s="4"/>
-    </row>
-    <row r="26">
-      <c r="D26" s="4"/>
-    </row>
-    <row r="27">
-      <c r="D27" s="4"/>
-    </row>
-    <row r="28">
-      <c r="D28" s="4"/>
-    </row>
-    <row r="29">
-      <c r="D29" s="4"/>
-    </row>
-    <row r="30">
-      <c r="D30" s="4"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="4"/>
-    </row>
-    <row r="32">
-      <c r="D32" s="4"/>
-    </row>
-    <row r="33">
-      <c r="D33" s="4"/>
-    </row>
-    <row r="34">
-      <c r="D34" s="4"/>
-    </row>
-    <row r="35">
-      <c r="D35" s="4"/>
-    </row>
-    <row r="36">
-      <c r="D36" s="4"/>
-    </row>
-    <row r="37">
-      <c r="D37" s="4"/>
-    </row>
-    <row r="38">
-      <c r="D38" s="4"/>
-    </row>
-    <row r="39">
-      <c r="D39" s="4"/>
-    </row>
-    <row r="40">
-      <c r="D40" s="4"/>
-    </row>
-    <row r="41">
-      <c r="D41" s="4"/>
-    </row>
-    <row r="42">
-      <c r="D42" s="4"/>
-    </row>
-    <row r="43">
-      <c r="D43" s="4"/>
-    </row>
-    <row r="44">
-      <c r="D44" s="4"/>
-    </row>
-    <row r="45">
-      <c r="D45" s="4"/>
-    </row>
-    <row r="46">
-      <c r="D46" s="4"/>
-    </row>
-    <row r="47">
-      <c r="D47" s="4"/>
-    </row>
-    <row r="48">
-      <c r="D48" s="4"/>
-    </row>
-    <row r="49">
-      <c r="D49" s="4"/>
-    </row>
-    <row r="50">
-      <c r="D50" s="4"/>
-    </row>
-    <row r="51">
-      <c r="D51" s="4"/>
-    </row>
-    <row r="52">
-      <c r="D52" s="4"/>
-    </row>
-    <row r="53">
-      <c r="D53" s="4"/>
-    </row>
-    <row r="54">
-      <c r="D54" s="4"/>
-    </row>
-    <row r="55">
-      <c r="D55" s="4"/>
-    </row>
-    <row r="56">
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57">
-      <c r="D57" s="4"/>
-    </row>
-    <row r="58">
-      <c r="D58" s="4"/>
-    </row>
-    <row r="59">
-      <c r="D59" s="4"/>
-    </row>
-    <row r="60">
-      <c r="D60" s="4"/>
-    </row>
-    <row r="61">
-      <c r="D61" s="4"/>
-    </row>
-    <row r="62">
-      <c r="D62" s="4"/>
-    </row>
-    <row r="63">
-      <c r="D63" s="4"/>
-    </row>
-    <row r="64">
-      <c r="D64" s="4"/>
-    </row>
-    <row r="65">
-      <c r="D65" s="4"/>
-    </row>
-    <row r="66">
-      <c r="D66" s="4"/>
-    </row>
-    <row r="67">
-      <c r="D67" s="4"/>
-    </row>
-    <row r="68">
-      <c r="D68" s="4"/>
-    </row>
-    <row r="69">
-      <c r="D69" s="4"/>
-    </row>
-    <row r="70">
-      <c r="D70" s="4"/>
     </row>
     <row r="71">
       <c r="D71" s="4"/>
@@ -3805,30 +4957,89 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
-      <c r="D3" s="4"/>
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="4">
-      <c r="D4" s="4"/>
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="5">
-      <c r="D5" s="4"/>
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6">
-      <c r="D6" s="4"/>
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="D7" s="4"/>
@@ -6858,17 +8069,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6879,16 +8090,16 @@
         <v>24.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -6899,16 +8110,16 @@
         <v>24.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -6919,16 +8130,16 @@
         <v>24.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6">
@@ -6939,16 +8150,16 @@
         <v>24.0</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -6959,16 +8170,16 @@
         <v>24.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -6979,16 +8190,16 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -6999,98 +8210,533 @@
         <v>24.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1">
+        <v>9.0</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1">
+        <v>11.0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="C13" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1">
+        <v>13.0</v>
+      </c>
+      <c r="C14" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1">
+        <v>14.0</v>
+      </c>
+      <c r="C15" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="C16" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1">
+        <v>16.0</v>
+      </c>
+      <c r="C17" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1">
+        <v>17.0</v>
+      </c>
+      <c r="C18" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11">
-      <c r="D11" s="4"/>
-    </row>
-    <row r="12">
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13">
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14">
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16">
-      <c r="D16" s="4"/>
-    </row>
-    <row r="17">
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18">
-      <c r="D18" s="4"/>
+      <c r="G18" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="19">
-      <c r="D19" s="4"/>
+      <c r="A19" s="1">
+        <v>18.0</v>
+      </c>
+      <c r="C19" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="20">
-      <c r="D20" s="4"/>
+      <c r="A20" s="1">
+        <v>19.0</v>
+      </c>
+      <c r="C20" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="21">
-      <c r="D21" s="4"/>
+      <c r="A21" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="C21" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="22">
-      <c r="D22" s="4"/>
+      <c r="A22" s="1">
+        <v>21.0</v>
+      </c>
+      <c r="C22" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="23">
-      <c r="D23" s="4"/>
+      <c r="A23" s="1">
+        <v>22.0</v>
+      </c>
+      <c r="C23" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="24">
-      <c r="D24" s="4"/>
+      <c r="A24" s="1">
+        <v>23.0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="25">
-      <c r="D25" s="4"/>
+      <c r="A25" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="26">
-      <c r="D26" s="4"/>
+      <c r="A26" s="1">
+        <v>25.0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="27">
-      <c r="D27" s="4"/>
+      <c r="A27" s="1">
+        <v>26.0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="28">
-      <c r="D28" s="4"/>
+      <c r="A28" s="1">
+        <v>27.0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
-      <c r="D29" s="4"/>
+      <c r="A29" s="1">
+        <v>28.0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="30">
-      <c r="D30" s="4"/>
+      <c r="A30" s="1">
+        <v>29.0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="31">
-      <c r="D31" s="4"/>
+      <c r="A31" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="32">
-      <c r="D32" s="4"/>
+      <c r="A32" s="1">
+        <v>31.0</v>
+      </c>
+      <c r="C32" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="33">
-      <c r="D33" s="4"/>
+      <c r="A33" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="C33" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="34">
-      <c r="D34" s="4"/>
+      <c r="A34" s="1">
+        <v>33.0</v>
+      </c>
+      <c r="C34" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="35">
-      <c r="D35" s="4"/>
+      <c r="A35" s="1">
+        <v>34.0</v>
+      </c>
+      <c r="C35" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="36">
-      <c r="D36" s="4"/>
+      <c r="A36" s="1">
+        <v>35.0</v>
+      </c>
+      <c r="C36" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="37">
       <c r="D37" s="4"/>
@@ -10033,7 +11679,7 @@
         <v>24.0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>12</v>
@@ -10057,6 +11703,63 @@
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="C6" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/songs.xlsx
+++ b/songs.xlsx
@@ -6,7 +6,10 @@
     <sheet state="visible" name="中文" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="英文" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="日文" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="台語" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="韓文" sheetId="4" r:id="rId8"/>
+    <sheet state="visible" name="台語" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="客語" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="粵語" sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="603" uniqueCount="363">
   <si>
     <t>id</t>
   </si>
@@ -40,18 +43,1002 @@
     <t>note</t>
   </si>
   <si>
+    <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=PZN1ns6OIyc</t>
   </si>
   <si>
+    <t>32:40</t>
+  </si>
+  <si>
+    <t>Breathe</t>
+  </si>
+  <si>
     <t>https://www.youtube.com/watch?v=QW_9qM7xpS8</t>
   </si>
   <si>
+    <t>Lee Hi</t>
+  </si>
+  <si>
+    <t>切歌</t>
+  </si>
+  <si>
+    <t>34:45</t>
+  </si>
+  <si>
+    <t>1:01:05</t>
+  </si>
+  <si>
+    <t>Miniskirt</t>
+  </si>
+  <si>
+    <t>AOA</t>
+  </si>
+  <si>
+    <t>3:02:49</t>
+  </si>
+  <si>
+    <t>ACT/アクト</t>
+  </si>
+  <si>
+    <t>大笑之歌</t>
+  </si>
+  <si>
+    <t>Giga, TeddyLoid, Daoko</t>
+  </si>
+  <si>
+    <t>四千金</t>
+  </si>
+  <si>
+    <t>Cover</t>
+  </si>
+  <si>
+    <t>32:29</t>
+  </si>
+  <si>
+    <t>7:16</t>
+  </si>
+  <si>
+    <t>JANE DOE</t>
+  </si>
+  <si>
+    <t>藍</t>
+  </si>
+  <si>
+    <t>米津玄師, 宇多田ヒカル</t>
+  </si>
+  <si>
+    <t>石白其</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>33:52</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>17:34</t>
+  </si>
+  <si>
+    <t>34:58</t>
+  </si>
+  <si>
+    <t>路過人間</t>
+  </si>
+  <si>
+    <t>37:38</t>
+  </si>
+  <si>
+    <t>郁可唯</t>
+  </si>
+  <si>
+    <t>40:59</t>
+  </si>
+  <si>
+    <t>IRIS OUT</t>
+  </si>
+  <si>
+    <t>米津玄師</t>
+  </si>
+  <si>
+    <t>21:56</t>
+  </si>
+  <si>
+    <t>半句再見</t>
+  </si>
+  <si>
+    <t>BAD GUY</t>
+  </si>
+  <si>
+    <t>孫燕姿</t>
+  </si>
+  <si>
+    <t>42:09</t>
+  </si>
+  <si>
+    <t>Billie Eilish</t>
+  </si>
+  <si>
+    <t>26:23</t>
+  </si>
+  <si>
+    <t>慢冷</t>
+  </si>
+  <si>
+    <t>44:43</t>
+  </si>
+  <si>
+    <t>革命道中</t>
+  </si>
+  <si>
+    <t>梁靜茹</t>
+  </si>
+  <si>
+    <t>アイナ・ジ・エンド</t>
+  </si>
+  <si>
+    <t>4:44:17</t>
+  </si>
+  <si>
+    <t>52:08</t>
+  </si>
+  <si>
+    <t>wish you were gay</t>
+  </si>
+  <si>
+    <t>孤獨的總和</t>
+  </si>
+  <si>
+    <t>4:20:12</t>
+  </si>
+  <si>
+    <t>吳汶芳</t>
+  </si>
+  <si>
+    <t>​​Bunny Girl</t>
+  </si>
+  <si>
+    <t>AKASAKI</t>
+  </si>
+  <si>
+    <t>57:34</t>
+  </si>
+  <si>
+    <t>挪威的森林</t>
+  </si>
+  <si>
+    <t>4:24:52</t>
+  </si>
+  <si>
+    <t>伍佰</t>
+  </si>
+  <si>
+    <t>プロポーズ</t>
+  </si>
+  <si>
+    <t>觀眾唱</t>
+  </si>
+  <si>
+    <t>なとり</t>
+  </si>
+  <si>
+    <t>4:48:35</t>
+  </si>
+  <si>
+    <t>4:27:12</t>
+  </si>
+  <si>
+    <t>鬼ノ宴(Demons Banquet)</t>
+  </si>
+  <si>
+    <t>1:03:45</t>
+  </si>
+  <si>
+    <t>i love you</t>
+  </si>
+  <si>
+    <t>友成空</t>
+  </si>
+  <si>
+    <t>買你</t>
+  </si>
+  <si>
+    <t>魏如萱</t>
+  </si>
+  <si>
+    <t>4:29:40</t>
+  </si>
+  <si>
+    <t>ほろよい</t>
+  </si>
+  <si>
+    <t>1:08:09</t>
+  </si>
+  <si>
+    <t>さんひ</t>
+  </si>
+  <si>
+    <t>我在紐約打電話給你</t>
+  </si>
+  <si>
+    <t>4:32:59</t>
+  </si>
+  <si>
+    <t>Overdose</t>
+  </si>
+  <si>
+    <t>1:12:27</t>
+  </si>
+  <si>
+    <t>開始懂了</t>
+  </si>
+  <si>
+    <t>5:04:18</t>
+  </si>
+  <si>
+    <t>1:17:44</t>
+  </si>
+  <si>
+    <t>4:35:26</t>
+  </si>
+  <si>
+    <t>我不難過</t>
+  </si>
+  <si>
+    <t>東京フラッシュ</t>
+  </si>
+  <si>
+    <t>Vaundy</t>
+  </si>
+  <si>
+    <t>1:18:47</t>
+  </si>
+  <si>
+    <t>4:38:47</t>
+  </si>
+  <si>
+    <t>CoCo</t>
+  </si>
+  <si>
+    <t>踊り子</t>
+  </si>
+  <si>
+    <t>O.T. Genasis</t>
+  </si>
+  <si>
+    <t>1:25:12</t>
+  </si>
+  <si>
+    <t>我懷念的</t>
+  </si>
+  <si>
+    <t>5:10:38</t>
+  </si>
+  <si>
+    <t>4:06:47</t>
+  </si>
+  <si>
+    <t>4:15:50</t>
+  </si>
+  <si>
+    <t>Playground</t>
+  </si>
+  <si>
+    <t>我們不一樣</t>
+  </si>
+  <si>
+    <t>大壯</t>
+  </si>
+  <si>
+    <t>Bea Miller</t>
+  </si>
+  <si>
+    <t>5:14:05</t>
+  </si>
+  <si>
+    <t>4:18:46</t>
+  </si>
+  <si>
+    <t>因為單身的緣故</t>
+  </si>
+  <si>
+    <t>李宗盛</t>
+  </si>
+  <si>
+    <t>5:15:38</t>
+  </si>
+  <si>
+    <t>4:53:54</t>
+  </si>
+  <si>
+    <t>5:20:33</t>
+  </si>
+  <si>
+    <t>偽顔</t>
+  </si>
+  <si>
+    <t>4:59:15</t>
+  </si>
+  <si>
+    <t>yama</t>
+  </si>
+  <si>
+    <t>微加幸福</t>
+  </si>
+  <si>
+    <t>5:21:48</t>
+  </si>
+  <si>
+    <t>5:47:00</t>
+  </si>
+  <si>
+    <t>偽顏</t>
+  </si>
+  <si>
+    <t>Santé</t>
+  </si>
+  <si>
+    <t>壞特</t>
+  </si>
+  <si>
+    <t>5:26:07</t>
+  </si>
+  <si>
+    <t>5:49:00</t>
+  </si>
+  <si>
+    <t>カタオモイ</t>
+  </si>
+  <si>
+    <t>Aimer</t>
+  </si>
+  <si>
+    <t>5:58:06</t>
+  </si>
+  <si>
+    <t>5:28:28</t>
+  </si>
+  <si>
+    <t>體面</t>
+  </si>
+  <si>
+    <t>NIGHT DANCER</t>
+  </si>
+  <si>
+    <t>于文文</t>
+  </si>
+  <si>
+    <t>imase</t>
+  </si>
+  <si>
+    <t>5:35:39</t>
+  </si>
+  <si>
+    <t>6:05:24</t>
+  </si>
+  <si>
+    <t>どうせ無くなるだけ</t>
+  </si>
+  <si>
+    <t>たかやん</t>
+  </si>
+  <si>
+    <t>捲菸</t>
+  </si>
+  <si>
+    <t>美秀集團</t>
+  </si>
+  <si>
+    <t>5:41:14</t>
+  </si>
+  <si>
+    <t>怪獣の花唄</t>
+  </si>
+  <si>
+    <t>6:11:14</t>
+  </si>
+  <si>
+    <t>5:43:10</t>
+  </si>
+  <si>
+    <t>ドライフラワー</t>
+  </si>
+  <si>
+    <t>優里</t>
+  </si>
+  <si>
+    <t>6:13:40</t>
+  </si>
+  <si>
+    <t>5:52:55</t>
+  </si>
+  <si>
+    <t>不可幸力</t>
+  </si>
+  <si>
+    <t>5:56:05</t>
+  </si>
+  <si>
+    <t>逆さまの蝶</t>
+  </si>
+  <si>
+    <t>SNoW / 地獄少女OP</t>
+  </si>
+  <si>
+    <t>6:03:12</t>
+  </si>
+  <si>
+    <t>香水</t>
+  </si>
+  <si>
+    <t>6:18:16</t>
+  </si>
+  <si>
+    <t>瑛人</t>
+  </si>
+  <si>
+    <t>6:24:26</t>
+  </si>
+  <si>
+    <t>3:29:16</t>
+  </si>
+  <si>
+    <t>刻在我心底的名字</t>
+  </si>
+  <si>
+    <t>白日</t>
+  </si>
+  <si>
+    <t>盧廣仲</t>
+  </si>
+  <si>
+    <t>King Gnu</t>
+  </si>
+  <si>
+    <t>6:36:21</t>
+  </si>
+  <si>
+    <t>幾分之幾</t>
+  </si>
+  <si>
+    <t>3:30:42</t>
+  </si>
+  <si>
+    <t>盧廣仲 / 花甲大人轉男孩</t>
+  </si>
+  <si>
+    <t>逢いたくていま</t>
+  </si>
+  <si>
+    <t>MISIA</t>
+  </si>
+  <si>
+    <t>6:46:04</t>
+  </si>
+  <si>
+    <t>明明就</t>
+  </si>
+  <si>
+    <t>3:39:48</t>
+  </si>
+  <si>
+    <t>周杰倫</t>
+  </si>
+  <si>
+    <t>ホウキ雲</t>
+  </si>
+  <si>
+    <t>RYTHEM / 烘焙王OP</t>
+  </si>
+  <si>
+    <t>6:53:33</t>
+  </si>
+  <si>
+    <t>3:43:29</t>
+  </si>
+  <si>
+    <t>7:03:34</t>
+  </si>
+  <si>
+    <t>3:48:22</t>
+  </si>
+  <si>
+    <t>7:08:22</t>
+  </si>
+  <si>
+    <t>3:53:31</t>
+  </si>
+  <si>
+    <t>39:47</t>
+  </si>
+  <si>
+    <t>寂寞寂寞就好</t>
+  </si>
+  <si>
+    <t>田馥甄</t>
+  </si>
+  <si>
+    <t>3:55:11</t>
+  </si>
+  <si>
+    <t>Bunny Girl</t>
+  </si>
+  <si>
+    <t>45:02</t>
+  </si>
+  <si>
+    <t>1:54:59</t>
+  </si>
+  <si>
+    <t>別の人の彼女になったよ</t>
+  </si>
+  <si>
+    <t>wacci</t>
+  </si>
+  <si>
+    <t>51:24</t>
+  </si>
+  <si>
+    <t>開夾</t>
+  </si>
+  <si>
+    <t>倒帶</t>
+  </si>
+  <si>
+    <t>蔡依林</t>
+  </si>
+  <si>
+    <t>1:09:59</t>
+  </si>
+  <si>
+    <t>なんか幸せ</t>
+  </si>
+  <si>
+    <t>56:42</t>
+  </si>
+  <si>
+    <t>烈火之炎OP</t>
+  </si>
+  <si>
+    <t>1:17:22</t>
+  </si>
+  <si>
+    <t>1:02:53</t>
+  </si>
+  <si>
+    <t>変わらないもの</t>
+  </si>
+  <si>
+    <t>奥華子 / 跳躍吧！時空少女</t>
+  </si>
+  <si>
+    <t>3:18:02</t>
+  </si>
+  <si>
+    <t>いのちの名前</t>
+  </si>
+  <si>
+    <t>木村弓 / 神隱少女</t>
+  </si>
+  <si>
+    <t>1:14:02</t>
+  </si>
+  <si>
+    <t>3:22:40</t>
+  </si>
+  <si>
+    <t>知道</t>
+  </si>
+  <si>
+    <t>シンデレラボーイ</t>
+  </si>
+  <si>
+    <t>石原慎也</t>
+  </si>
+  <si>
+    <t>郭靜</t>
+  </si>
+  <si>
+    <t>3:28:24</t>
+  </si>
+  <si>
+    <t>たばこ</t>
+  </si>
+  <si>
+    <t>ダズビー</t>
+  </si>
+  <si>
+    <t>1:19:07</t>
+  </si>
+  <si>
+    <t>曖昧</t>
+  </si>
+  <si>
+    <t>3:35:00</t>
+  </si>
+  <si>
+    <t>楊丞琳</t>
+  </si>
+  <si>
+    <t>Hero's Come Back!!</t>
+  </si>
+  <si>
+    <t>nobodyknows+ / 火影忍者疾風傳OP</t>
+  </si>
+  <si>
+    <t>1:26:53</t>
+  </si>
+  <si>
+    <t>小幸運</t>
+  </si>
+  <si>
+    <t>3:41:11</t>
+  </si>
+  <si>
+    <t>the WORLD</t>
+  </si>
+  <si>
+    <t>1:33:50</t>
+  </si>
+  <si>
+    <t>NIGHTMARE / 死亡筆記本OP</t>
+  </si>
+  <si>
+    <t>喜劇收場</t>
+  </si>
+  <si>
+    <t>3:42:35</t>
+  </si>
+  <si>
+    <t>1:40:01</t>
+  </si>
+  <si>
+    <t>不夠成熟</t>
+  </si>
+  <si>
+    <t>BY2</t>
+  </si>
+  <si>
+    <t>1:47:22</t>
+  </si>
+  <si>
+    <t>分手後不要做朋友</t>
+  </si>
+  <si>
+    <t>梁文音</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=G_5bOFykGPs</t>
+  </si>
+  <si>
+    <t>1:59:55</t>
+  </si>
+  <si>
+    <t>我不配</t>
+  </si>
+  <si>
+    <t>2:05:01</t>
+  </si>
+  <si>
+    <t>2:14:03</t>
+  </si>
+  <si>
+    <t>老鼠愛大米</t>
+  </si>
+  <si>
+    <t>王啟文</t>
+  </si>
+  <si>
+    <t>2:16:55</t>
+  </si>
+  <si>
+    <t>下一個天亮</t>
+  </si>
+  <si>
+    <t>2:22:12</t>
+  </si>
+  <si>
+    <t>像天堂的懸崖</t>
+  </si>
+  <si>
+    <t>李佳薇</t>
+  </si>
+  <si>
+    <t>2:27:49</t>
+  </si>
+  <si>
+    <t>有一種悲傷</t>
+  </si>
+  <si>
+    <t>A-Lin</t>
+  </si>
+  <si>
+    <t>2:35:24</t>
+  </si>
+  <si>
+    <t>聽見下雨的聲音</t>
+  </si>
+  <si>
+    <t>魏如昀</t>
+  </si>
+  <si>
+    <t>2:40:30</t>
+  </si>
+  <si>
+    <t>落雨聲</t>
+  </si>
+  <si>
+    <t>江蕙</t>
+  </si>
+  <si>
+    <t>2:50:00</t>
+  </si>
+  <si>
+    <t>你就不要想起我</t>
+  </si>
+  <si>
+    <t>2:54:45</t>
+  </si>
+  <si>
+    <t>Bのリベンジ</t>
+  </si>
+  <si>
+    <t>福栗, 真理果</t>
+  </si>
+  <si>
+    <t>3:00:18</t>
+  </si>
+  <si>
+    <t>Cover, 合唱</t>
+  </si>
+  <si>
+    <t>3:11:22</t>
+  </si>
+  <si>
+    <t>3:22:00</t>
+  </si>
+  <si>
+    <t>雨愛</t>
+  </si>
+  <si>
+    <t>4:01:19</t>
+  </si>
+  <si>
+    <t>4:09:57</t>
+  </si>
+  <si>
+    <t>渺小</t>
+  </si>
+  <si>
+    <t>4:16:28</t>
+  </si>
+  <si>
+    <t>我想我不會愛你</t>
+  </si>
+  <si>
+    <t>4:19:07</t>
+  </si>
+  <si>
+    <t>年輪說</t>
+  </si>
+  <si>
+    <t>4:23:01</t>
+  </si>
+  <si>
+    <t>夢醒時分</t>
+  </si>
+  <si>
+    <t>8:47</t>
+  </si>
+  <si>
+    <t>愛過的樣子</t>
+  </si>
+  <si>
+    <t>王艷薇</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>14:27</t>
+  </si>
+  <si>
+    <t>25:09</t>
+  </si>
+  <si>
+    <t>如果我不知道</t>
+  </si>
+  <si>
+    <t>張語噥</t>
+  </si>
+  <si>
+    <t>25:49</t>
+  </si>
+  <si>
+    <t>29:05</t>
+  </si>
+  <si>
+    <t>在迦納共和國離婚</t>
+  </si>
+  <si>
+    <t>菲道爾 &amp; 大穎</t>
+  </si>
+  <si>
+    <t>33:29</t>
+  </si>
+  <si>
+    <t>40:42</t>
+  </si>
+  <si>
+    <t>自導自演</t>
+  </si>
+  <si>
+    <t>慢慢說</t>
+  </si>
+  <si>
+    <t>45:40</t>
+  </si>
+  <si>
+    <t>太陽與地球</t>
+  </si>
+  <si>
+    <t>50:58</t>
+  </si>
+  <si>
+    <t>52:33</t>
+  </si>
+  <si>
+    <t>改編</t>
+  </si>
+  <si>
+    <t>55:15</t>
+  </si>
+  <si>
+    <t>水星記</t>
+  </si>
+  <si>
+    <t>郭頂</t>
+  </si>
+  <si>
+    <t>1:00:20</t>
+  </si>
+  <si>
+    <t>1:06:09</t>
+  </si>
+  <si>
+    <t>愛情怎麼了嗎</t>
+  </si>
+  <si>
+    <t>1:10:44</t>
+  </si>
+  <si>
+    <t>1:16:37</t>
+  </si>
+  <si>
+    <t>我的歌聲裡</t>
+  </si>
+  <si>
+    <t>曲婉婷</t>
+  </si>
+  <si>
+    <t>1:21:35</t>
+  </si>
+  <si>
+    <t>舅媽</t>
+  </si>
+  <si>
+    <t>巴大雄</t>
+  </si>
+  <si>
+    <t>1:26:58</t>
+  </si>
+  <si>
+    <t>帶我走</t>
+  </si>
+  <si>
+    <t>1:31:34</t>
+  </si>
+  <si>
+    <t>片段</t>
+  </si>
+  <si>
+    <t>1:36:36</t>
+  </si>
+  <si>
+    <t>1:37:35</t>
+  </si>
+  <si>
+    <t>1:43:06</t>
+  </si>
+  <si>
+    <t>1:47:01</t>
+  </si>
+  <si>
+    <t>她說</t>
+  </si>
+  <si>
+    <t>林俊傑</t>
+  </si>
+  <si>
+    <t>2:03:06</t>
+  </si>
+  <si>
+    <t>2:07:16</t>
+  </si>
+  <si>
+    <t>2:11:07</t>
+  </si>
+  <si>
+    <t>2:11:50</t>
+  </si>
+  <si>
+    <t>27:28</t>
+  </si>
+  <si>
+    <t>我會好好的</t>
+  </si>
+  <si>
+    <t>王心凌</t>
+  </si>
+  <si>
+    <t>37:49</t>
+  </si>
+  <si>
+    <t>天黑黑</t>
+  </si>
+  <si>
+    <t>42:49</t>
+  </si>
+  <si>
+    <t>遇見</t>
+  </si>
+  <si>
+    <t>47:34</t>
+  </si>
+  <si>
+    <t>53:10</t>
+  </si>
+  <si>
+    <t>我想要佔據你</t>
+  </si>
+  <si>
+    <t>告五人</t>
+  </si>
+  <si>
+    <t>1:04:58</t>
+  </si>
+  <si>
+    <t>修練愛情</t>
+  </si>
+  <si>
+    <t>2:48:50</t>
+  </si>
+  <si>
+    <t>逆光</t>
+  </si>
+  <si>
+    <t>3:06:56</t>
+  </si>
+  <si>
+    <t>知花</t>
+  </si>
+  <si>
+    <t>合唱</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zbOsJbnkhyk</t>
+  </si>
+  <si>
+    <t>神崎アルファ</t>
+  </si>
+  <si>
     <t>47:01</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=HqAD0u-Q-Uk</t>
-  </si>
-  <si>
     <t>含淚跳恰恰</t>
   </si>
   <si>
@@ -70,15 +1057,9 @@
     <t>6:01:13</t>
   </si>
   <si>
-    <t>香水</t>
-  </si>
-  <si>
     <t>江志豐 vs 張秀卿</t>
   </si>
   <si>
-    <t>切歌</t>
-  </si>
-  <si>
     <t>6:09:58</t>
   </si>
   <si>
@@ -97,664 +1078,34 @@
     <t>猪哥亮</t>
   </si>
   <si>
-    <t>大笑之歌</t>
-  </si>
-  <si>
-    <t>BAD GUY</t>
-  </si>
-  <si>
-    <t>四千金</t>
-  </si>
-  <si>
-    <t>ACT/アクト</t>
-  </si>
-  <si>
-    <t>Billie Eilish</t>
-  </si>
-  <si>
-    <t>Cover</t>
-  </si>
-  <si>
-    <t>Giga, TeddyLoid, Daoko</t>
-  </si>
-  <si>
-    <t>7:16</t>
-  </si>
-  <si>
-    <t>藍</t>
-  </si>
-  <si>
-    <t>4:44:17</t>
-  </si>
-  <si>
-    <t>石白其</t>
-  </si>
-  <si>
-    <t>wish you were gay</t>
-  </si>
-  <si>
-    <t>32:29</t>
-  </si>
-  <si>
-    <t>JANE DOE</t>
-  </si>
-  <si>
-    <t>米津玄師, 宇多田ヒカル</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>NG</t>
-  </si>
-  <si>
-    <t>4:48:35</t>
-  </si>
-  <si>
-    <t>i love you</t>
-  </si>
-  <si>
-    <t>17:34</t>
-  </si>
-  <si>
-    <t>33:52</t>
-  </si>
-  <si>
-    <t>路過人間</t>
-  </si>
-  <si>
-    <t>5:04:18</t>
-  </si>
-  <si>
-    <t>郁可唯</t>
-  </si>
-  <si>
-    <t>CoCo</t>
-  </si>
-  <si>
-    <t>O.T. Genasis</t>
-  </si>
-  <si>
-    <t>21:56</t>
-  </si>
-  <si>
-    <t>半句再見</t>
-  </si>
-  <si>
-    <t>孫燕姿</t>
-  </si>
-  <si>
-    <t>4:06:47</t>
-  </si>
-  <si>
-    <t>34:58</t>
-  </si>
-  <si>
-    <t>Playground</t>
-  </si>
-  <si>
-    <t>Bea Miller</t>
-  </si>
-  <si>
-    <t>26:23</t>
-  </si>
-  <si>
-    <t>慢冷</t>
-  </si>
-  <si>
-    <t>梁靜茹</t>
-  </si>
-  <si>
-    <t>37:38</t>
-  </si>
-  <si>
-    <t>52:08</t>
-  </si>
-  <si>
-    <t>孤獨的總和</t>
-  </si>
-  <si>
-    <t>吳汶芳</t>
-  </si>
-  <si>
-    <t>57:34</t>
-  </si>
-  <si>
-    <t>挪威的森林</t>
-  </si>
-  <si>
-    <t>40:59</t>
-  </si>
-  <si>
-    <t>伍佰</t>
-  </si>
-  <si>
-    <t>IRIS OUT</t>
-  </si>
-  <si>
-    <t>觀眾唱</t>
-  </si>
-  <si>
-    <t>米津玄師</t>
-  </si>
-  <si>
-    <t>1:03:45</t>
-  </si>
-  <si>
-    <t>買你</t>
-  </si>
-  <si>
-    <t>魏如萱</t>
-  </si>
-  <si>
-    <t>42:09</t>
-  </si>
-  <si>
-    <t>1:08:09</t>
-  </si>
-  <si>
-    <t>我在紐約打電話給你</t>
-  </si>
-  <si>
-    <t>44:43</t>
-  </si>
-  <si>
-    <t>1:12:27</t>
-  </si>
-  <si>
-    <t>革命道中</t>
-  </si>
-  <si>
-    <t>開始懂了</t>
-  </si>
-  <si>
-    <t>アイナ・ジ・エンド</t>
-  </si>
-  <si>
-    <t>1:17:44</t>
-  </si>
-  <si>
-    <t>我不難過</t>
-  </si>
-  <si>
-    <t>4:20:12</t>
-  </si>
-  <si>
-    <t>​​Bunny Girl</t>
-  </si>
-  <si>
-    <t>AKASAKI</t>
-  </si>
-  <si>
-    <t>1:18:47</t>
-  </si>
-  <si>
-    <t>4:24:52</t>
-  </si>
-  <si>
-    <t>プロポーズ</t>
-  </si>
-  <si>
-    <t>1:25:12</t>
-  </si>
-  <si>
-    <t>なとり</t>
-  </si>
-  <si>
-    <t>我懷念的</t>
-  </si>
-  <si>
-    <t>4:15:50</t>
-  </si>
-  <si>
-    <t>4:27:12</t>
-  </si>
-  <si>
-    <t>我們不一樣</t>
-  </si>
-  <si>
-    <t>鬼ノ宴(Demons Banquet)</t>
-  </si>
-  <si>
-    <t>大壯</t>
-  </si>
-  <si>
-    <t>友成空</t>
-  </si>
-  <si>
-    <t>4:18:46</t>
-  </si>
-  <si>
-    <t>因為單身的緣故</t>
-  </si>
-  <si>
-    <t>李宗盛</t>
-  </si>
-  <si>
-    <t>4:29:40</t>
-  </si>
-  <si>
-    <t>ほろよい</t>
-  </si>
-  <si>
-    <t>さんひ</t>
-  </si>
-  <si>
-    <t>4:53:54</t>
-  </si>
-  <si>
-    <t>4:59:15</t>
-  </si>
-  <si>
-    <t>4:32:59</t>
-  </si>
-  <si>
-    <t>微加幸福</t>
-  </si>
-  <si>
-    <t>Overdose</t>
-  </si>
-  <si>
-    <t>5:47:00</t>
-  </si>
-  <si>
-    <t>Santé</t>
-  </si>
-  <si>
-    <t>?te 壞特</t>
-  </si>
-  <si>
-    <t>4:35:26</t>
-  </si>
-  <si>
-    <t>5:49:00</t>
-  </si>
-  <si>
-    <t>東京フラッシュ</t>
-  </si>
-  <si>
-    <t>Vaundy</t>
-  </si>
-  <si>
-    <t>5:58:06</t>
-  </si>
-  <si>
-    <t>體面</t>
-  </si>
-  <si>
-    <t>于文文</t>
-  </si>
-  <si>
-    <t>4:38:47</t>
-  </si>
-  <si>
-    <t>踊り子</t>
-  </si>
-  <si>
-    <t>6:05:24</t>
-  </si>
-  <si>
-    <t>捲菸</t>
-  </si>
-  <si>
-    <t>美秀集團</t>
-  </si>
-  <si>
-    <t>6:11:14</t>
-  </si>
-  <si>
-    <t>5:10:38</t>
-  </si>
-  <si>
-    <t>6:13:40</t>
-  </si>
-  <si>
-    <t>5:14:05</t>
-  </si>
-  <si>
-    <t>6:18:16</t>
-  </si>
-  <si>
-    <t>6:24:26</t>
-  </si>
-  <si>
-    <t>刻在我心底的名字</t>
-  </si>
-  <si>
-    <t>盧廣仲</t>
-  </si>
-  <si>
-    <t>5:15:38</t>
-  </si>
-  <si>
-    <t>6:36:21</t>
-  </si>
-  <si>
-    <t>幾分之幾</t>
-  </si>
-  <si>
-    <t>盧廣仲 / 花甲大人轉男孩</t>
-  </si>
-  <si>
-    <t>6:46:04</t>
-  </si>
-  <si>
-    <t>明明就</t>
-  </si>
-  <si>
-    <t>周杰倫</t>
-  </si>
-  <si>
-    <t>5:20:33</t>
-  </si>
-  <si>
-    <t>偽顔</t>
-  </si>
-  <si>
-    <t>6:53:33</t>
-  </si>
-  <si>
-    <t>yama</t>
-  </si>
-  <si>
-    <t>7:03:34</t>
-  </si>
-  <si>
-    <t>7:08:22</t>
-  </si>
-  <si>
-    <t>5:21:48</t>
-  </si>
-  <si>
-    <t>偽顏</t>
-  </si>
-  <si>
-    <t>39:47</t>
-  </si>
-  <si>
-    <t>寂寞寂寞就好</t>
-  </si>
-  <si>
-    <t>田馥甄</t>
-  </si>
-  <si>
-    <t>45:02</t>
-  </si>
-  <si>
-    <t>5:26:07</t>
-  </si>
-  <si>
-    <t>51:24</t>
-  </si>
-  <si>
-    <t>カタオモイ</t>
-  </si>
-  <si>
-    <t>倒帶</t>
-  </si>
-  <si>
-    <t>蔡依林</t>
-  </si>
-  <si>
-    <t>Aimer</t>
-  </si>
-  <si>
-    <t>56:42</t>
-  </si>
-  <si>
-    <t>5:28:28</t>
-  </si>
-  <si>
-    <t>1:02:53</t>
-  </si>
-  <si>
-    <t>NIGHT DANCER</t>
-  </si>
-  <si>
-    <t>imase</t>
-  </si>
-  <si>
-    <t>1:14:02</t>
-  </si>
-  <si>
-    <t>知道</t>
-  </si>
-  <si>
-    <t>郭靜</t>
-  </si>
-  <si>
-    <t>5:35:39</t>
-  </si>
-  <si>
-    <t>どうせ無くなるだけ</t>
-  </si>
-  <si>
-    <t>1:19:07</t>
-  </si>
-  <si>
-    <t>曖昧</t>
-  </si>
-  <si>
-    <t>たかやん</t>
-  </si>
-  <si>
-    <t>楊丞琳</t>
-  </si>
-  <si>
-    <t>1:26:53</t>
-  </si>
-  <si>
-    <t>小幸運</t>
-  </si>
-  <si>
-    <t>5:41:14</t>
-  </si>
-  <si>
-    <t>怪獣の花唄</t>
-  </si>
-  <si>
-    <t>1:33:50</t>
-  </si>
-  <si>
-    <t>喜劇收場</t>
-  </si>
-  <si>
-    <t>1:40:01</t>
-  </si>
-  <si>
-    <t>5:43:10</t>
-  </si>
-  <si>
-    <t>不夠成熟</t>
-  </si>
-  <si>
-    <t>BY2</t>
-  </si>
-  <si>
-    <t>ドライフラワー</t>
-  </si>
-  <si>
-    <t>優里</t>
-  </si>
-  <si>
-    <t>1:47:22</t>
-  </si>
-  <si>
-    <t>分手後不要做朋友</t>
-  </si>
-  <si>
-    <t>梁文音</t>
-  </si>
-  <si>
-    <t>1:59:55</t>
-  </si>
-  <si>
-    <t>5:52:55</t>
-  </si>
-  <si>
-    <t>我不配</t>
-  </si>
-  <si>
-    <t>不可幸力</t>
-  </si>
-  <si>
-    <t>2:05:01</t>
-  </si>
-  <si>
-    <t>2:14:03</t>
-  </si>
-  <si>
-    <t>老鼠愛大米</t>
-  </si>
-  <si>
-    <t>王啟文</t>
-  </si>
-  <si>
-    <t>2:16:55</t>
-  </si>
-  <si>
-    <t>下一個天亮</t>
-  </si>
-  <si>
-    <t>2:22:12</t>
-  </si>
-  <si>
-    <t>像天堂的懸崖</t>
-  </si>
-  <si>
-    <t>李佳薇</t>
-  </si>
-  <si>
-    <t>2:27:49</t>
-  </si>
-  <si>
-    <t>有一種悲傷</t>
-  </si>
-  <si>
-    <t>A-Lin</t>
-  </si>
-  <si>
-    <t>2:35:24</t>
-  </si>
-  <si>
-    <t>聽見下雨的聲音</t>
-  </si>
-  <si>
-    <t>魏如昀</t>
-  </si>
-  <si>
-    <t>2:40:30</t>
-  </si>
-  <si>
-    <t>落雨聲</t>
-  </si>
-  <si>
-    <t>江蕙</t>
-  </si>
-  <si>
-    <t>2:50:00</t>
-  </si>
-  <si>
-    <t>你就不要想起我</t>
-  </si>
-  <si>
-    <t>2:54:45</t>
-  </si>
-  <si>
-    <t>3:00:18</t>
-  </si>
-  <si>
-    <t>3:11:22</t>
-  </si>
-  <si>
-    <t>3:22:00</t>
-  </si>
-  <si>
-    <t>雨愛</t>
-  </si>
-  <si>
-    <t>4:01:19</t>
-  </si>
-  <si>
-    <t>4:09:57</t>
-  </si>
-  <si>
-    <t>渺小</t>
-  </si>
-  <si>
-    <t>5:56:05</t>
-  </si>
-  <si>
-    <t>逆さまの蝶</t>
-  </si>
-  <si>
-    <t>SNoW / 地獄少女OP</t>
-  </si>
-  <si>
-    <t>4:16:28</t>
-  </si>
-  <si>
-    <t>我想我不會愛你</t>
-  </si>
-  <si>
-    <t>6:03:12</t>
-  </si>
-  <si>
-    <t>4:19:07</t>
-  </si>
-  <si>
-    <t>年輪說</t>
-  </si>
-  <si>
-    <t>瑛人</t>
-  </si>
-  <si>
-    <t>4:23:01</t>
-  </si>
-  <si>
-    <t>3:29:16</t>
-  </si>
-  <si>
-    <t>夢醒時分</t>
-  </si>
-  <si>
-    <t>白日</t>
-  </si>
-  <si>
-    <t>King Gnu</t>
-  </si>
-  <si>
-    <t>3:30:42</t>
-  </si>
-  <si>
-    <t>逢いたくていま</t>
-  </si>
-  <si>
-    <t>MISIA</t>
-  </si>
-  <si>
-    <t>3:39:48</t>
-  </si>
-  <si>
-    <t>ホウキ雲</t>
-  </si>
-  <si>
-    <t>RYTHEM / 烘焙王OP</t>
-  </si>
-  <si>
-    <t>3:43:29</t>
-  </si>
-  <si>
-    <t>3:48:22</t>
-  </si>
-  <si>
-    <t>3:53:31</t>
-  </si>
-  <si>
-    <t>3:55:11</t>
-  </si>
-  <si>
-    <t>Bunny Girl</t>
+    <t>4:20:39</t>
+  </si>
+  <si>
+    <t>一支小雨傘</t>
+  </si>
+  <si>
+    <t>洪榮宏</t>
+  </si>
+  <si>
+    <t>1:31:53</t>
+  </si>
+  <si>
+    <t>大番薯</t>
+  </si>
+  <si>
+    <t>童謠</t>
+  </si>
+  <si>
+    <t>3:27:05</t>
+  </si>
+  <si>
+    <t>黃瑋中</t>
+  </si>
+  <si>
+    <t>3:28:00</t>
+  </si>
+  <si>
+    <t>47:26</t>
   </si>
 </sst>
 </file>
@@ -827,6 +1178,18 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -1066,17 +1429,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -1087,13 +1450,13 @@
         <v>24.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -1104,13 +1467,13 @@
         <v>24.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -1121,13 +1484,13 @@
         <v>24.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -1138,13 +1501,13 @@
         <v>24.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -1155,13 +1518,13 @@
         <v>24.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8">
@@ -1172,13 +1535,13 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9">
@@ -1189,16 +1552,16 @@
         <v>24.0</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -1209,7 +1572,7 @@
         <v>24.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>75</v>
@@ -1226,10 +1589,10 @@
         <v>24.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>76</v>
@@ -1243,13 +1606,13 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -1260,16 +1623,16 @@
         <v>24.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1280,13 +1643,13 @@
         <v>24.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -1297,13 +1660,13 @@
         <v>24.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16">
@@ -1314,16 +1677,16 @@
         <v>38.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
@@ -1334,16 +1697,16 @@
         <v>38.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -1354,13 +1717,13 @@
         <v>38.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19">
@@ -1371,13 +1734,13 @@
         <v>38.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -1388,16 +1751,16 @@
         <v>38.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -1408,13 +1771,13 @@
         <v>38.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
@@ -1425,16 +1788,16 @@
         <v>38.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1445,13 +1808,13 @@
         <v>38.0</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24">
@@ -1462,16 +1825,16 @@
         <v>38.0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1482,13 +1845,13 @@
         <v>38.0</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26">
@@ -1499,13 +1862,13 @@
         <v>38.0</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27">
@@ -1516,13 +1879,13 @@
         <v>38.0</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28">
@@ -1533,13 +1896,13 @@
         <v>38.0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29">
@@ -1550,13 +1913,13 @@
         <v>38.0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>140</v>
+        <v>166</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30">
@@ -1567,13 +1930,13 @@
         <v>38.0</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31">
@@ -1584,13 +1947,13 @@
         <v>38.0</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -1601,13 +1964,13 @@
         <v>38.0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33">
@@ -1618,13 +1981,13 @@
         <v>43.0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34">
@@ -1635,13 +1998,13 @@
         <v>43.0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>154</v>
+        <v>183</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35">
@@ -1652,13 +2015,13 @@
         <v>43.0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>158</v>
+        <v>189</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>159</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36">
@@ -1669,13 +2032,13 @@
         <v>43.0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -1686,13 +2049,13 @@
         <v>43.0</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -1703,13 +2066,13 @@
         <v>43.0</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>166</v>
+        <v>202</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39">
@@ -1720,13 +2083,13 @@
         <v>43.0</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40">
@@ -1737,13 +2100,13 @@
         <v>43.0</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>175</v>
+        <v>217</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41">
@@ -1754,13 +2117,13 @@
         <v>43.0</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>179</v>
+        <v>221</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>180</v>
+        <v>223</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42">
@@ -1771,13 +2134,13 @@
         <v>43.0</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>183</v>
+        <v>226</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>184</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43">
@@ -1788,13 +2151,13 @@
         <v>43.0</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44">
@@ -1805,13 +2168,13 @@
         <v>43.0</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>190</v>
+        <v>232</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45">
@@ -1822,13 +2185,13 @@
         <v>43.0</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>142</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46">
@@ -1839,16 +2202,16 @@
         <v>43.0</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>196</v>
+        <v>236</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47">
@@ -1859,13 +2222,13 @@
         <v>43.0</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>198</v>
+        <v>238</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>199</v>
+        <v>239</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>168</v>
+        <v>207</v>
       </c>
     </row>
     <row r="48">
@@ -1876,13 +2239,13 @@
         <v>43.0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>202</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49">
@@ -1893,13 +2256,13 @@
         <v>43.0</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>203</v>
+        <v>243</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
     </row>
     <row r="50">
@@ -1910,13 +2273,13 @@
         <v>43.0</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>208</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51">
@@ -1927,13 +2290,13 @@
         <v>43.0</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>209</v>
+        <v>249</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>211</v>
+        <v>251</v>
       </c>
     </row>
     <row r="52">
@@ -1944,13 +2307,13 @@
         <v>43.0</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="53">
@@ -1961,13 +2324,13 @@
         <v>43.0</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>214</v>
+        <v>254</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
@@ -1978,13 +2341,13 @@
         <v>43.0</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55">
@@ -1995,16 +2358,16 @@
         <v>43.0</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56">
@@ -2015,13 +2378,13 @@
         <v>43.0</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57">
@@ -2032,7 +2395,7 @@
         <v>43.0</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>75</v>
@@ -2049,13 +2412,13 @@
         <v>43.0</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59">
@@ -2066,16 +2429,16 @@
         <v>43.0</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>225</v>
+        <v>265</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>226</v>
+        <v>266</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="60">
@@ -2086,16 +2449,16 @@
         <v>43.0</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>228</v>
+        <v>267</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -2106,131 +2469,676 @@
         <v>43.0</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>231</v>
+        <v>269</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1">
+        <v>61.0</v>
+      </c>
+      <c r="C62" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1">
+        <v>62.0</v>
+      </c>
+      <c r="C63" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1">
+        <v>63.0</v>
+      </c>
+      <c r="C64" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1">
+        <v>64.0</v>
+      </c>
+      <c r="C65" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1">
+        <v>65.0</v>
+      </c>
+      <c r="C66" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1">
+        <v>66.0</v>
+      </c>
+      <c r="C67" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1">
+        <v>67.0</v>
+      </c>
+      <c r="C68" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1">
+        <v>68.0</v>
+      </c>
+      <c r="C69" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1">
+        <v>69.0</v>
+      </c>
+      <c r="C70" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="71">
-      <c r="D71" s="4"/>
+      <c r="A71" s="1">
+        <v>70.0</v>
+      </c>
+      <c r="C71" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="72">
-      <c r="D72" s="4"/>
+      <c r="A72" s="1">
+        <v>71.0</v>
+      </c>
+      <c r="C72" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="73">
-      <c r="D73" s="4"/>
+      <c r="A73" s="1">
+        <v>72.0</v>
+      </c>
+      <c r="C73" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="74">
-      <c r="D74" s="4"/>
+      <c r="A74" s="1">
+        <v>73.0</v>
+      </c>
+      <c r="C74" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="75">
-      <c r="D75" s="4"/>
+      <c r="A75" s="1">
+        <v>74.0</v>
+      </c>
+      <c r="C75" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="76">
-      <c r="D76" s="4"/>
+      <c r="A76" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="C76" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="77">
-      <c r="D77" s="4"/>
+      <c r="A77" s="1">
+        <v>76.0</v>
+      </c>
+      <c r="C77" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="78">
-      <c r="D78" s="4"/>
+      <c r="A78" s="1">
+        <v>77.0</v>
+      </c>
+      <c r="C78" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="79">
-      <c r="D79" s="4"/>
+      <c r="A79" s="1">
+        <v>78.0</v>
+      </c>
+      <c r="C79" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="80">
-      <c r="D80" s="4"/>
+      <c r="A80" s="1">
+        <v>79.0</v>
+      </c>
+      <c r="C80" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="81">
-      <c r="D81" s="4"/>
+      <c r="A81" s="1">
+        <v>80.0</v>
+      </c>
+      <c r="C81" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="82">
-      <c r="D82" s="4"/>
+      <c r="A82" s="1">
+        <v>81.0</v>
+      </c>
+      <c r="C82" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="83">
-      <c r="D83" s="4"/>
+      <c r="A83" s="1">
+        <v>82.0</v>
+      </c>
+      <c r="C83" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>291</v>
+      </c>
     </row>
     <row r="84">
-      <c r="D84" s="4"/>
+      <c r="A84" s="1">
+        <v>83.0</v>
+      </c>
+      <c r="C84" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>314</v>
+      </c>
     </row>
     <row r="85">
-      <c r="D85" s="4"/>
+      <c r="A85" s="1">
+        <v>84.0</v>
+      </c>
+      <c r="C85" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="86">
-      <c r="D86" s="4"/>
+      <c r="A86" s="1">
+        <v>85.0</v>
+      </c>
+      <c r="C86" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="87">
-      <c r="D87" s="4"/>
+      <c r="A87" s="1">
+        <v>86.0</v>
+      </c>
+      <c r="C87" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="88">
-      <c r="D88" s="4"/>
+      <c r="A88" s="1">
+        <v>87.0</v>
+      </c>
+      <c r="C88" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="89">
-      <c r="D89" s="4"/>
+      <c r="A89" s="1">
+        <v>88.0</v>
+      </c>
+      <c r="C89" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>321</v>
+      </c>
     </row>
     <row r="90">
-      <c r="D90" s="4"/>
+      <c r="A90" s="1">
+        <v>89.0</v>
+      </c>
+      <c r="C90" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="91">
-      <c r="D91" s="4"/>
+      <c r="A91" s="1">
+        <v>90.0</v>
+      </c>
+      <c r="C91" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="92">
-      <c r="D92" s="4"/>
+      <c r="A92" s="1">
+        <v>91.0</v>
+      </c>
+      <c r="C92" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="93">
-      <c r="D93" s="4"/>
+      <c r="A93" s="1">
+        <v>92.0</v>
+      </c>
+      <c r="C93" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>329</v>
+      </c>
     </row>
     <row r="94">
-      <c r="D94" s="4"/>
+      <c r="A94" s="1">
+        <v>93.0</v>
+      </c>
+      <c r="C94" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="95">
-      <c r="D95" s="4"/>
+      <c r="A95" s="1">
+        <v>94.0</v>
+      </c>
+      <c r="C95" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="96">
-      <c r="D96" s="4"/>
+      <c r="A96" s="1">
+        <v>95.0</v>
+      </c>
+      <c r="C96" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>214</v>
+      </c>
     </row>
     <row r="97">
-      <c r="D97" s="4"/>
+      <c r="A97" s="1">
+        <v>96.0</v>
+      </c>
+      <c r="C97" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="98">
-      <c r="D98" s="4"/>
-    </row>
-    <row r="99">
-      <c r="D99" s="4"/>
-    </row>
-    <row r="100">
-      <c r="D100" s="4"/>
-    </row>
-    <row r="101">
-      <c r="D101" s="4"/>
-    </row>
-    <row r="102">
-      <c r="D102" s="4"/>
-    </row>
-    <row r="103">
-      <c r="D103" s="4"/>
-    </row>
-    <row r="104">
-      <c r="D104" s="4"/>
-    </row>
-    <row r="105">
-      <c r="D105" s="4"/>
-    </row>
-    <row r="106">
-      <c r="D106" s="4"/>
-    </row>
-    <row r="107">
-      <c r="D107" s="4"/>
-    </row>
-    <row r="108">
-      <c r="D108" s="4"/>
+      <c r="A98" s="1">
+        <v>97.0</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="109">
       <c r="D109" s="4"/>
@@ -4910,12 +5818,25 @@
     </row>
     <row r="1001">
       <c r="D1001" s="4"/>
+    </row>
+    <row r="1002">
+      <c r="D1002" s="4"/>
+    </row>
+    <row r="1003">
+      <c r="D1003" s="4"/>
+    </row>
+    <row r="1004">
+      <c r="D1004" s="4"/>
+    </row>
+    <row r="1005">
+      <c r="D1005" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="B98"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -4957,17 +5878,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -4978,13 +5899,13 @@
         <v>38.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -4995,13 +5916,13 @@
         <v>38.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -5012,13 +5933,13 @@
         <v>38.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
@@ -5029,16 +5950,16 @@
         <v>43.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>59</v>
+        <v>105</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -8069,17 +8990,17 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3">
@@ -8090,16 +9011,16 @@
         <v>24.0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -8110,16 +9031,16 @@
         <v>24.0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -8130,16 +9051,16 @@
         <v>24.0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -8150,16 +9071,16 @@
         <v>24.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -8170,16 +9091,16 @@
         <v>24.0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -8190,16 +9111,16 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -8210,16 +9131,16 @@
         <v>24.0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -8230,13 +9151,13 @@
         <v>38.0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>88</v>
+        <v>60</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -8247,16 +9168,16 @@
         <v>38.0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -8267,16 +9188,16 @@
         <v>38.0</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>74</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -8287,16 +9208,16 @@
         <v>38.0</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -8307,16 +9228,16 @@
         <v>38.0</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -8327,16 +9248,16 @@
         <v>38.0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -8347,13 +9268,13 @@
         <v>38.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -8364,16 +9285,16 @@
         <v>38.0</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -8384,16 +9305,16 @@
         <v>38.0</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -8404,13 +9325,13 @@
         <v>38.0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -8421,16 +9342,16 @@
         <v>38.0</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>143</v>
+        <v>112</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -8441,16 +9362,16 @@
         <v>38.0</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -8461,16 +9382,16 @@
         <v>38.0</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -8481,13 +9402,13 @@
         <v>38.0</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
@@ -8498,13 +9419,13 @@
         <v>38.0</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
@@ -8515,16 +9436,16 @@
         <v>38.0</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>177</v>
+        <v>138</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>178</v>
+        <v>139</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -8535,16 +9456,16 @@
         <v>38.0</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>182</v>
+        <v>141</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>185</v>
+        <v>142</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
@@ -8555,16 +9476,16 @@
         <v>38.0</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>191</v>
+        <v>145</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>193</v>
+        <v>146</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -8575,16 +9496,16 @@
         <v>38.0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>222</v>
+        <v>147</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>224</v>
+        <v>149</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -8595,16 +9516,16 @@
         <v>38.0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>227</v>
+        <v>150</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>151</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>230</v>
+        <v>153</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -8615,16 +9536,16 @@
         <v>43.0</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>232</v>
+        <v>155</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>234</v>
+        <v>157</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>235</v>
+        <v>159</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -8635,13 +9556,13 @@
         <v>43.0</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>236</v>
+        <v>162</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>238</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32">
@@ -8652,16 +9573,16 @@
         <v>43.0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>239</v>
+        <v>168</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>240</v>
+        <v>170</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -8672,13 +9593,13 @@
         <v>43.0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34">
@@ -8689,13 +9610,13 @@
         <v>43.0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
@@ -8706,16 +9627,16 @@
         <v>43.0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>244</v>
+        <v>177</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -8726,47 +9647,196 @@
         <v>43.0</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
-      <c r="D37" s="4"/>
+      <c r="A37" s="1">
+        <v>36.0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="38">
-      <c r="D38" s="4"/>
+      <c r="A38" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="39">
-      <c r="D39" s="4"/>
+      <c r="A39" s="1">
+        <v>38.0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="40">
-      <c r="D40" s="4"/>
+      <c r="A40" s="1">
+        <v>39.0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="41">
-      <c r="D41" s="4"/>
+      <c r="A41" s="1">
+        <v>40.0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="42">
-      <c r="D42" s="4"/>
+      <c r="A42" s="1">
+        <v>41.0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="43">
-      <c r="D43" s="4"/>
+      <c r="A43" s="1">
+        <v>42.0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>216</v>
+      </c>
     </row>
     <row r="44">
-      <c r="D44" s="4"/>
+      <c r="A44" s="1">
+        <v>43.0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="45">
-      <c r="D45" s="4"/>
+      <c r="A45" s="1">
+        <v>44.0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="46">
-      <c r="D46" s="4"/>
+      <c r="A46" s="1">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="47">
       <c r="D47" s="4"/>
@@ -11626,15 +12696,13 @@
     </row>
     <row r="999">
       <c r="D999" s="4"/>
-    </row>
-    <row r="1000">
-      <c r="D1000" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
+    <hyperlink r:id="rId2" ref="B46"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -11676,16 +12744,19 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="1">
-        <v>24.0</v>
+        <v>75.0</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -11693,16 +12764,19 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="1">
-        <v>24.0</v>
+        <v>75.0</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -11710,19 +12784,16 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="1">
-        <v>38.0</v>
+        <v>75.0</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -11730,19 +12801,131 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="1">
+        <v>75.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>24.0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="1">
         <v>38.0</v>
       </c>
+      <c r="D4" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>38.0</v>
+      </c>
       <c r="D5" s="2" t="s">
-        <v>21</v>
+        <v>347</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>348</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>349</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -11753,13 +12936,180 @@
         <v>43.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>350</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>351</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>26</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1">
+        <v>6.0</v>
+      </c>
+      <c r="C7" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>355</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C2" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="C3" s="1">
+        <v>59.0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1">
+        <v>3.0</v>
+      </c>
+      <c r="C4" s="1">
+        <v>60.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/songs.xlsx
+++ b/songs.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="297">
   <si>
     <t>id</t>
   </si>
@@ -28,22 +28,46 @@
     <t>artist</t>
   </si>
   <si>
+    <t>ko1</t>
+  </si>
+  <si>
     <t>zh1</t>
   </si>
   <si>
+    <t>Breathe</t>
+  </si>
+  <si>
+    <t>Lee Hi</t>
+  </si>
+  <si>
+    <t>ko2</t>
+  </si>
+  <si>
+    <t>en1</t>
+  </si>
+  <si>
     <t>大笑之歌</t>
   </si>
   <si>
-    <t>en1</t>
-  </si>
-  <si>
     <t>BAD GUY</t>
   </si>
   <si>
+    <t>Miniskirt</t>
+  </si>
+  <si>
+    <t>Billie Eilish</t>
+  </si>
+  <si>
+    <t>AOA</t>
+  </si>
+  <si>
     <t>四千金</t>
   </si>
   <si>
-    <t>Billie Eilish</t>
+    <t>en2</t>
+  </si>
+  <si>
+    <t>wish you were gay</t>
   </si>
   <si>
     <t>zh2</t>
@@ -52,13 +76,13 @@
     <t>藍</t>
   </si>
   <si>
-    <t>en2</t>
+    <t>en3</t>
   </si>
   <si>
     <t>石白其</t>
   </si>
   <si>
-    <t>wish you were gay</t>
+    <t>i love you</t>
   </si>
   <si>
     <t>zh3</t>
@@ -67,178 +91,274 @@
     <t>路過人間</t>
   </si>
   <si>
+    <t>en4</t>
+  </si>
+  <si>
+    <t>ja1</t>
+  </si>
+  <si>
     <t>郁可唯</t>
   </si>
   <si>
-    <t>en3</t>
+    <t>CoCo</t>
+  </si>
+  <si>
+    <t>O.T. Genasis</t>
   </si>
   <si>
     <t>zh4</t>
   </si>
   <si>
-    <t>i love you</t>
+    <t>ACT/アクト</t>
   </si>
   <si>
     <t>半句再見</t>
   </si>
   <si>
+    <t>en5</t>
+  </si>
+  <si>
     <t>孫燕姿</t>
   </si>
   <si>
+    <t>Giga, TeddyLoid, Daoko</t>
+  </si>
+  <si>
+    <t>Playground</t>
+  </si>
+  <si>
     <t>zh5</t>
   </si>
   <si>
-    <t>en4</t>
+    <t>ja2</t>
+  </si>
+  <si>
+    <t>Bea Miller</t>
   </si>
   <si>
     <t>慢冷</t>
   </si>
   <si>
-    <t>CoCo</t>
+    <t>JANE DOE</t>
   </si>
   <si>
     <t>梁靜茹</t>
   </si>
   <si>
-    <t>O.T. Genasis</t>
+    <t>米津玄師, 宇多田ヒカル</t>
   </si>
   <si>
     <t>zh6</t>
   </si>
   <si>
+    <t>ja3</t>
+  </si>
+  <si>
     <t>孤獨的總和</t>
   </si>
   <si>
-    <t>en5</t>
+    <t>IRIS OUT</t>
   </si>
   <si>
     <t>吳汶芳</t>
   </si>
   <si>
-    <t>Playground</t>
+    <t>米津玄師</t>
   </si>
   <si>
     <t>zh7</t>
   </si>
   <si>
-    <t>Bea Miller</t>
-  </si>
-  <si>
     <t>挪威的森林</t>
   </si>
   <si>
     <t>伍佰</t>
   </si>
   <si>
+    <t>ja4</t>
+  </si>
+  <si>
+    <t>革命道中</t>
+  </si>
+  <si>
     <t>zh8</t>
   </si>
   <si>
+    <t>アイナ・ジ・エンド</t>
+  </si>
+  <si>
     <t>買你</t>
   </si>
   <si>
+    <t>ja5</t>
+  </si>
+  <si>
     <t>魏如萱</t>
   </si>
   <si>
+    <t>Bunny Girl</t>
+  </si>
+  <si>
     <t>zh9</t>
   </si>
   <si>
     <t>我在紐約打電話給你</t>
   </si>
   <si>
+    <t>AKASAKI</t>
+  </si>
+  <si>
     <t>zh10</t>
   </si>
   <si>
+    <t>ja6</t>
+  </si>
+  <si>
     <t>開始懂了</t>
   </si>
   <si>
+    <t>プロポーズ</t>
+  </si>
+  <si>
+    <t>なとり</t>
+  </si>
+  <si>
     <t>zh11</t>
   </si>
   <si>
     <t>我不難過</t>
   </si>
   <si>
+    <t>ja7</t>
+  </si>
+  <si>
+    <t>鬼ノ宴(Demons Banquet)</t>
+  </si>
+  <si>
+    <t>友成空</t>
+  </si>
+  <si>
     <t>zh12</t>
   </si>
   <si>
     <t>我懷念的</t>
   </si>
   <si>
+    <t>ja8</t>
+  </si>
+  <si>
+    <t>ほろよい</t>
+  </si>
+  <si>
     <t>zh13</t>
   </si>
   <si>
     <t>我們不一樣</t>
   </si>
   <si>
+    <t>さんひ</t>
+  </si>
+  <si>
     <t>大壯</t>
   </si>
   <si>
+    <t>ja9</t>
+  </si>
+  <si>
     <t>zh14</t>
   </si>
   <si>
+    <t>Overdose</t>
+  </si>
+  <si>
     <t>因為單身的緣故</t>
   </si>
   <si>
     <t>李宗盛</t>
   </si>
   <si>
+    <t>ja10</t>
+  </si>
+  <si>
     <t>zh15</t>
   </si>
   <si>
+    <t>東京フラッシュ</t>
+  </si>
+  <si>
     <t>微加幸福</t>
   </si>
   <si>
+    <t>Vaundy</t>
+  </si>
+  <si>
+    <t>ja11</t>
+  </si>
+  <si>
     <t>zh16</t>
   </si>
   <si>
+    <t>踊り子</t>
+  </si>
+  <si>
     <t>Santé</t>
   </si>
   <si>
     <t>壞特</t>
   </si>
   <si>
+    <t>ja12</t>
+  </si>
+  <si>
     <t>zh17</t>
   </si>
   <si>
+    <t>偽顏</t>
+  </si>
+  <si>
     <t>體面</t>
   </si>
   <si>
+    <t>yama</t>
+  </si>
+  <si>
     <t>于文文</t>
   </si>
   <si>
     <t>zh18</t>
   </si>
   <si>
-    <t>ja1</t>
+    <t>ja13</t>
   </si>
   <si>
     <t>捲菸</t>
   </si>
   <si>
+    <t>カタオモイ</t>
+  </si>
+  <si>
     <t>美秀集團</t>
   </si>
   <si>
-    <t>ACT/アクト</t>
-  </si>
-  <si>
-    <t>Giga, TeddyLoid, Daoko</t>
+    <t>Aimer</t>
   </si>
   <si>
     <t>zh19</t>
   </si>
   <si>
+    <t>ja14</t>
+  </si>
+  <si>
     <t>刻在我心底的名字</t>
   </si>
   <si>
-    <t>ja2</t>
+    <t>NIGHT DANCER</t>
   </si>
   <si>
     <t>盧廣仲</t>
   </si>
   <si>
-    <t>JANE DOE</t>
-  </si>
-  <si>
-    <t>米津玄師, 宇多田ヒカル</t>
+    <t>imase</t>
   </si>
   <si>
     <t>zh20</t>
@@ -247,115 +367,97 @@
     <t>幾分之幾</t>
   </si>
   <si>
-    <t>ja3</t>
+    <t>ja15</t>
   </si>
   <si>
     <t>盧廣仲 / 花甲大人轉男孩</t>
   </si>
   <si>
-    <t>IRIS OUT</t>
+    <t>どうせ無くなるだけ</t>
   </si>
   <si>
     <t>zh21</t>
   </si>
   <si>
-    <t>米津玄師</t>
-  </si>
-  <si>
     <t>明明就</t>
   </si>
   <si>
+    <t>たかやん</t>
+  </si>
+  <si>
     <t>周杰倫</t>
   </si>
   <si>
-    <t>ja4</t>
-  </si>
-  <si>
-    <t>革命道中</t>
-  </si>
-  <si>
     <t>zh22</t>
   </si>
   <si>
-    <t>アイナ・ジ・エンド</t>
+    <t>ja16</t>
   </si>
   <si>
     <t>寂寞寂寞就好</t>
   </si>
   <si>
+    <t>怪獣の花唄</t>
+  </si>
+  <si>
     <t>田馥甄</t>
   </si>
   <si>
-    <t>ja5</t>
-  </si>
-  <si>
-    <t>Bunny Girl</t>
-  </si>
-  <si>
     <t>zh23</t>
   </si>
   <si>
-    <t>AKASAKI</t>
-  </si>
-  <si>
     <t>倒帶</t>
   </si>
   <si>
     <t>蔡依林</t>
   </si>
   <si>
-    <t>ja6</t>
+    <t>ja17</t>
   </si>
   <si>
     <t>zh24</t>
   </si>
   <si>
-    <t>プロポーズ</t>
+    <t>ドライフラワー</t>
   </si>
   <si>
     <t>知道</t>
   </si>
   <si>
-    <t>なとり</t>
-  </si>
-  <si>
     <t>郭靜</t>
   </si>
   <si>
+    <t>優里</t>
+  </si>
+  <si>
     <t>zh25</t>
   </si>
   <si>
-    <t>ja7</t>
-  </si>
-  <si>
     <t>曖昧</t>
   </si>
   <si>
-    <t>鬼ノ宴(Demons Banquet)</t>
+    <t>ja18</t>
   </si>
   <si>
     <t>楊丞琳</t>
   </si>
   <si>
-    <t>友成空</t>
-  </si>
-  <si>
-    <t>ja8</t>
-  </si>
-  <si>
-    <t>ほろよい</t>
+    <t>不可幸力</t>
   </si>
   <si>
     <t>zh26</t>
   </si>
   <si>
-    <t>さんひ</t>
-  </si>
-  <si>
     <t>小幸運</t>
   </si>
   <si>
-    <t>ja9</t>
+    <t>ja19</t>
+  </si>
+  <si>
+    <t>逆さまの蝶</t>
+  </si>
+  <si>
+    <t>SNoW / 地獄少女OP</t>
   </si>
   <si>
     <t>zh27</t>
@@ -364,7 +466,13 @@
     <t>喜劇收場</t>
   </si>
   <si>
-    <t>Overdose</t>
+    <t>ja20</t>
+  </si>
+  <si>
+    <t>香水</t>
+  </si>
+  <si>
+    <t>瑛人</t>
   </si>
   <si>
     <t>zh28</t>
@@ -373,399 +481,291 @@
     <t>不夠成熟</t>
   </si>
   <si>
-    <t>ko1</t>
-  </si>
-  <si>
-    <t>ja10</t>
+    <t>ja21</t>
   </si>
   <si>
     <t>BY2</t>
   </si>
   <si>
-    <t>Breathe</t>
-  </si>
-  <si>
-    <t>東京フラッシュ</t>
-  </si>
-  <si>
-    <t>Lee Hi</t>
+    <t>白日</t>
+  </si>
+  <si>
+    <t>King Gnu</t>
   </si>
   <si>
     <t>zh29</t>
   </si>
   <si>
-    <t>Vaundy</t>
-  </si>
-  <si>
     <t>分手後不要做朋友</t>
   </si>
   <si>
-    <t>ko2</t>
-  </si>
-  <si>
-    <t>ja11</t>
+    <t>ja22</t>
   </si>
   <si>
     <t>梁文音</t>
   </si>
   <si>
-    <t>Miniskirt</t>
-  </si>
-  <si>
-    <t>踊り子</t>
+    <t>逢いたくていま</t>
   </si>
   <si>
     <t>zh30</t>
   </si>
   <si>
-    <t>AOA</t>
-  </si>
-  <si>
-    <t>ja12</t>
+    <t>MISIA</t>
   </si>
   <si>
     <t>我不配</t>
   </si>
   <si>
-    <t>偽顏</t>
-  </si>
-  <si>
-    <t>yama</t>
-  </si>
-  <si>
-    <t>ja13</t>
+    <t>ja23</t>
+  </si>
+  <si>
+    <t>ホウキ雲</t>
   </si>
   <si>
     <t>zh31</t>
   </si>
   <si>
-    <t>カタオモイ</t>
+    <t>RYTHEM / 烘焙王OP</t>
   </si>
   <si>
     <t>老鼠愛大米</t>
   </si>
   <si>
-    <t>Aimer</t>
-  </si>
-  <si>
     <t>王啟文</t>
   </si>
   <si>
-    <t>ja14</t>
+    <t>ja24</t>
+  </si>
+  <si>
+    <t>別の人の彼女になったよ</t>
   </si>
   <si>
     <t>zh32</t>
   </si>
   <si>
-    <t>NIGHT DANCER</t>
+    <t>wacci</t>
   </si>
   <si>
     <t>下一個天亮</t>
   </si>
   <si>
-    <t>imase</t>
-  </si>
-  <si>
-    <t>ja15</t>
+    <t>ja25</t>
+  </si>
+  <si>
+    <t>なんか幸せ</t>
   </si>
   <si>
     <t>zh33</t>
   </si>
   <si>
-    <t>どうせ無くなるだけ</t>
-  </si>
-  <si>
     <t>像天堂的懸崖</t>
   </si>
   <si>
-    <t>たかやん</t>
+    <t>烈火之炎OP</t>
   </si>
   <si>
     <t>李佳薇</t>
   </si>
   <si>
+    <t>ja26</t>
+  </si>
+  <si>
     <t>zh34</t>
   </si>
   <si>
-    <t>ja16</t>
+    <t>変わらないもの</t>
   </si>
   <si>
     <t>有一種悲傷</t>
   </si>
   <si>
-    <t>怪獣の花唄</t>
+    <t>奥華子 / 跳躍吧！時空少女</t>
   </si>
   <si>
     <t>A-Lin</t>
   </si>
   <si>
+    <t>ja27</t>
+  </si>
+  <si>
     <t>zh35</t>
   </si>
   <si>
-    <t>ja17</t>
+    <t>いのちの名前</t>
   </si>
   <si>
     <t>聽見下雨的聲音</t>
   </si>
   <si>
-    <t>ドライフラワー</t>
+    <t>木村弓 / 神隱少女</t>
   </si>
   <si>
     <t>魏如昀</t>
   </si>
   <si>
-    <t>優里</t>
+    <t>ja28</t>
   </si>
   <si>
     <t>zh36</t>
   </si>
   <si>
-    <t>ja18</t>
+    <t>シンデレラボーイ</t>
   </si>
   <si>
     <t>你就不要想起我</t>
   </si>
   <si>
-    <t>不可幸力</t>
+    <t>石原慎也</t>
   </si>
   <si>
     <t>zh37</t>
   </si>
   <si>
-    <t>ja19</t>
+    <t>ja29</t>
+  </si>
+  <si>
+    <t>たばこ</t>
   </si>
   <si>
     <t>雨愛</t>
   </si>
   <si>
-    <t>逆さまの蝶</t>
-  </si>
-  <si>
-    <t>SNoW / 地獄少女OP</t>
+    <t>ダズビー</t>
+  </si>
+  <si>
+    <t>ja30</t>
   </si>
   <si>
     <t>zh38</t>
   </si>
   <si>
-    <t>ja20</t>
-  </si>
-  <si>
     <t>渺小</t>
   </si>
   <si>
-    <t>香水</t>
-  </si>
-  <si>
-    <t>瑛人</t>
+    <t>Hero's Come Back!!</t>
+  </si>
+  <si>
+    <t>nobodyknows+ / 火影忍者疾風傳OP</t>
   </si>
   <si>
     <t>zh39</t>
   </si>
   <si>
-    <t>ja21</t>
-  </si>
-  <si>
     <t>我想我不會愛你</t>
   </si>
   <si>
-    <t>白日</t>
-  </si>
-  <si>
-    <t>King Gnu</t>
+    <t>ja31</t>
+  </si>
+  <si>
+    <t>the WORLD</t>
   </si>
   <si>
     <t>zh40</t>
   </si>
   <si>
-    <t>ja22</t>
+    <t>NIGHTMARE / 死亡筆記本OP</t>
   </si>
   <si>
     <t>年輪說</t>
   </si>
   <si>
-    <t>逢いたくていま</t>
+    <t>ja32</t>
   </si>
   <si>
     <t>zh41</t>
   </si>
   <si>
-    <t>MISIA</t>
-  </si>
-  <si>
     <t>夢醒時分</t>
   </si>
   <si>
-    <t>ja23</t>
+    <t>Bのリベンジ</t>
+  </si>
+  <si>
+    <t>B小町 ルビー(伊駒ゆりえ)、有馬かな(潘めぐみ)、MEMちょ(大久保瑠美)</t>
   </si>
   <si>
     <t>zh42</t>
   </si>
   <si>
-    <t>ホウキ雲</t>
-  </si>
-  <si>
     <t>愛過的樣子</t>
   </si>
   <si>
-    <t>RYTHEM / 烘焙王OP</t>
-  </si>
-  <si>
     <t>王艷薇</t>
   </si>
   <si>
     <t>zh43</t>
   </si>
   <si>
-    <t>ja24</t>
-  </si>
-  <si>
     <t>如果我不知道</t>
   </si>
   <si>
-    <t>別の人の彼女になったよ</t>
-  </si>
-  <si>
     <t>張語噥</t>
   </si>
   <si>
-    <t>wacci</t>
-  </si>
-  <si>
     <t>zh44</t>
   </si>
   <si>
-    <t>ja25</t>
-  </si>
-  <si>
     <t>在迦納共和國離婚</t>
   </si>
   <si>
-    <t>なんか幸せ</t>
-  </si>
-  <si>
     <t>菲道爾 &amp; 大穎</t>
   </si>
   <si>
-    <t>烈火之炎OP</t>
-  </si>
-  <si>
     <t>zh45</t>
   </si>
   <si>
-    <t>ja26</t>
-  </si>
-  <si>
     <t>自導自演</t>
   </si>
   <si>
-    <t>変わらないもの</t>
-  </si>
-  <si>
     <t>慢慢說</t>
   </si>
   <si>
-    <t>奥華子 / 跳躍吧！時空少女</t>
-  </si>
-  <si>
     <t>zh46</t>
   </si>
   <si>
     <t>太陽與地球</t>
   </si>
   <si>
-    <t>ja27</t>
-  </si>
-  <si>
-    <t>いのちの名前</t>
-  </si>
-  <si>
-    <t>木村弓 / 神隱少女</t>
-  </si>
-  <si>
     <t>zh47</t>
   </si>
   <si>
-    <t>ja28</t>
-  </si>
-  <si>
     <t>水星記</t>
   </si>
   <si>
-    <t>シンデレラボーイ</t>
-  </si>
-  <si>
-    <t>石原慎也</t>
-  </si>
-  <si>
     <t>郭頂</t>
   </si>
   <si>
-    <t>ja29</t>
-  </si>
-  <si>
-    <t>たばこ</t>
-  </si>
-  <si>
     <t>zh48</t>
   </si>
   <si>
-    <t>ダズビー</t>
-  </si>
-  <si>
     <t>愛情怎麼了嗎</t>
   </si>
   <si>
-    <t>ja30</t>
-  </si>
-  <si>
     <t>zh49</t>
   </si>
   <si>
-    <t>Hero's Come Back!!</t>
-  </si>
-  <si>
     <t>我的歌聲裡</t>
   </si>
   <si>
-    <t>nobodyknows+ / 火影忍者疾風傳OP</t>
-  </si>
-  <si>
     <t>曲婉婷</t>
   </si>
   <si>
-    <t>ja31</t>
-  </si>
-  <si>
     <t>zh50</t>
   </si>
   <si>
-    <t>the WORLD</t>
-  </si>
-  <si>
     <t>舅媽</t>
   </si>
   <si>
-    <t>NIGHTMARE / 死亡筆記本OP</t>
-  </si>
-  <si>
     <t>巴大雄</t>
   </si>
   <si>
-    <t>ja32</t>
-  </si>
-  <si>
     <t>zh51</t>
   </si>
   <si>
-    <t>Bのリベンジ</t>
-  </si>
-  <si>
     <t>帶我走</t>
   </si>
   <si>
-    <t>B小町 ルビー(伊駒ゆりえ)、有馬かな(潘めぐみ)、MEMちょ(大久保瑠美)</t>
-  </si>
-  <si>
     <t>zh52</t>
   </si>
   <si>
@@ -815,6 +815,24 @@
   </si>
   <si>
     <t>逆光</t>
+  </si>
+  <si>
+    <t>zh59</t>
+  </si>
+  <si>
+    <t>我們都傻</t>
+  </si>
+  <si>
+    <t>zh60</t>
+  </si>
+  <si>
+    <t>幸福在歌唱</t>
+  </si>
+  <si>
+    <t>zh61</t>
+  </si>
+  <si>
+    <t>甲乙丙丁</t>
   </si>
   <si>
     <t>nan1</t>
@@ -1194,563 +1212,563 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>58</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>141</v>
+        <v>170</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>157</v>
+        <v>186</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>159</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>172</v>
+        <v>203</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>182</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>187</v>
+        <v>216</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="s">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>202</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="s">
-        <v>204</v>
+        <v>228</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>105</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53">
@@ -1783,7 +1801,7 @@
         <v>256</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56">
@@ -1794,7 +1812,7 @@
         <v>258</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
@@ -1827,7 +1845,40 @@
         <v>265</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -1855,57 +1906,57 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1933,354 +1984,354 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>102</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>106</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>137</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>125</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>181</v>
+        <v>154</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>184</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>201</v>
+        <v>173</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>203</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>205</v>
+        <v>177</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>209</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>211</v>
+        <v>183</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>215</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>236</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -2308,24 +2359,24 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>121</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>127</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>130</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>133</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2353,79 +2404,79 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -2453,13 +2504,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
   </sheetData>
@@ -2487,13 +2538,13 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
